--- a/Analysis/exports/screener_2026-08-31.xlsx
+++ b/Analysis/exports/screener_2026-08-31.xlsx
@@ -507,7 +507,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-31 12:41</t>
+          <t>2026-08-31 15:00</t>
         </is>
       </c>
     </row>
@@ -566,7 +566,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
     <col width="21" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="7" customWidth="1" min="5" max="5"/>
@@ -656,27 +656,27 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>NYKAA</t>
+          <t>AUROPHARMA</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Nykaa</t>
+          <t>Aurobindo Pharma</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>E-Commerce</t>
+          <t>Pharma</t>
         </is>
       </c>
       <c r="D2" s="4" t="n">
-        <v>340.9</v>
+        <v>1684.6</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>65</v>
+        <v>56.1</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>0.45</v>
+        <v>1.77</v>
       </c>
       <c r="G2" s="4" t="inlineStr">
         <is>
@@ -705,42 +705,42 @@
       </c>
       <c r="L2" s="4" t="inlineStr">
         <is>
-          <t>Prime</t>
+          <t>Sweet Spot</t>
         </is>
       </c>
       <c r="M2" s="5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N2" s="4" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:NYKAA</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:AUROPHARMA</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
         <is>
-          <t>HYUNDAI</t>
+          <t>BAJAJ-AUTO</t>
         </is>
       </c>
       <c r="B3" s="6" t="inlineStr">
         <is>
-          <t>Hyundai Motor India</t>
+          <t>Bajaj Auto</t>
         </is>
       </c>
       <c r="C3" s="6" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Automobile</t>
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>2256.2</v>
+        <v>11995</v>
       </c>
       <c r="E3" s="6" t="n">
-        <v>61.3</v>
+        <v>61.8</v>
       </c>
       <c r="F3" s="6" t="n">
-        <v>0.6</v>
+        <v>1.16</v>
       </c>
       <c r="G3" s="6" t="inlineStr">
         <is>
@@ -759,7 +759,7 @@
       </c>
       <c r="J3" s="6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K3" s="6" t="inlineStr">
@@ -777,34 +777,34 @@
       </c>
       <c r="N3" s="6" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:HYUNDAI</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:BAJAJ-AUTO</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>SOLARINDS</t>
+          <t>NYKAA</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>Solar Industries</t>
+          <t>Nykaa</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>E-Commerce</t>
         </is>
       </c>
       <c r="D4" s="4" t="n">
-        <v>20349</v>
+        <v>339.3</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>68.8</v>
+        <v>63.9</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>0.39</v>
+        <v>0.71</v>
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
@@ -823,7 +823,7 @@
       </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K4" s="4" t="inlineStr">
@@ -841,34 +841,34 @@
       </c>
       <c r="N4" s="4" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:SOLARINDS</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:NYKAA</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>AUROPHARMA</t>
+          <t>AUBANK</t>
         </is>
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma</t>
+          <t>AU Small Finance Bank</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>Pharma</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>1699.1</v>
+        <v>1077.9</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>58.9</v>
+        <v>52.1</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>1.05</v>
+        <v>0.53</v>
       </c>
       <c r="G5" s="6" t="inlineStr">
         <is>
@@ -877,12 +877,12 @@
       </c>
       <c r="H5" s="6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I5" s="6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J5" s="6" t="inlineStr">
@@ -900,39 +900,39 @@
           <t>Sweet Spot</t>
         </is>
       </c>
-      <c r="M5" s="7" t="n">
-        <v>8</v>
+      <c r="M5" s="5" t="n">
+        <v>9</v>
       </c>
       <c r="N5" s="6" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:AUROPHARMA</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:AUBANK</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>BAJAJ-AUTO</t>
+          <t>SOLARINDS</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Bajaj Auto</t>
+          <t>Solar Industries</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>Automobile</t>
+          <t>Capital Goods</t>
         </is>
       </c>
       <c r="D6" s="4" t="n">
-        <v>11998</v>
+        <v>20242</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>61.9</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.79</v>
+        <v>0.49</v>
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
@@ -964,39 +964,39 @@
           <t>Sweet Spot</t>
         </is>
       </c>
-      <c r="M6" s="7" t="n">
-        <v>8</v>
+      <c r="M6" s="5" t="n">
+        <v>9</v>
       </c>
       <c r="N6" s="4" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:BAJAJ-AUTO</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:SOLARINDS</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>COFORGE</t>
+          <t>ATHERENERG</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>Coforge</t>
+          <t>Ather Energy</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>Automobile</t>
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>1983.3</v>
+        <v>1687.3</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>68.8</v>
+        <v>67.2</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>0.66</v>
+        <v>2.7</v>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
@@ -1015,7 +1015,7 @@
       </c>
       <c r="J7" s="6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K7" s="6" t="inlineStr">
@@ -1028,39 +1028,39 @@
           <t>Sweet Spot</t>
         </is>
       </c>
-      <c r="M7" s="7" t="n">
+      <c r="M7" s="5" t="n">
         <v>8</v>
       </c>
       <c r="N7" s="6" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:COFORGE</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:ATHERENERG</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>CDSL</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>CDSL</t>
+          <t>Laurus Labs</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Pharma</t>
         </is>
       </c>
       <c r="D8" s="4" t="n">
-        <v>1392.7</v>
+        <v>1874.1</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>60.1</v>
+        <v>52.2</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.58</v>
+        <v>2.51</v>
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J8" s="4" t="inlineStr">
@@ -1092,39 +1092,39 @@
           <t>Sweet Spot</t>
         </is>
       </c>
-      <c r="M8" s="7" t="n">
+      <c r="M8" s="5" t="n">
         <v>8</v>
       </c>
       <c r="N8" s="4" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:CDSL</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:LAURUSLABS</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>LODHA</t>
+          <t>ICICIBANK</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>Lodha Developers</t>
+          <t>ICICI Bank</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D9" s="6" t="n">
-        <v>1232.4</v>
+        <v>1442.8</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>53.8</v>
+        <v>54.6</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>0.57</v>
+        <v>1.28</v>
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="J9" s="6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K9" s="6" t="inlineStr">
@@ -1156,39 +1156,39 @@
           <t>Sweet Spot</t>
         </is>
       </c>
-      <c r="M9" s="7" t="n">
+      <c r="M9" s="5" t="n">
         <v>8</v>
       </c>
       <c r="N9" s="6" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:LODHA</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:ICICIBANK</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>ZYDUSLIFE</t>
+          <t>HYUNDAI</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Zydus Lifesciences</t>
+          <t>Hyundai Motor India</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>Pharma</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D10" s="4" t="n">
-        <v>1164.7</v>
+        <v>2248.7</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>44.9</v>
+        <v>59.5</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>0.42</v>
+        <v>0.78</v>
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
@@ -1220,48 +1220,48 @@
           <t>Sweet Spot</t>
         </is>
       </c>
-      <c r="M10" s="7" t="n">
+      <c r="M10" s="5" t="n">
         <v>8</v>
       </c>
       <c r="N10" s="4" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:ZYDUSLIFE</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:HYUNDAI</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>APOLLOHOSP</t>
+          <t>MCX</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>Apollo Hospitals</t>
+          <t>MCX</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>8853.5</v>
+        <v>3340.1</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>55.1</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>0.41</v>
+        <v>0.68</v>
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H11" s="6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I11" s="6" t="inlineStr">
@@ -1271,7 +1271,7 @@
       </c>
       <c r="J11" s="6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K11" s="6" t="inlineStr">
@@ -1284,43 +1284,43 @@
           <t>Sweet Spot</t>
         </is>
       </c>
-      <c r="M11" s="7" t="n">
+      <c r="M11" s="5" t="n">
         <v>8</v>
       </c>
       <c r="N11" s="6" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:APOLLOHOSP</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:MCX</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>BHEL</t>
+          <t>UNOMINDA</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>BHEL</t>
+          <t>UNO Minda</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Automobile</t>
         </is>
       </c>
       <c r="D12" s="4" t="n">
-        <v>434.5</v>
+        <v>1280.8</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>67.5</v>
+        <v>51.9</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>0.39</v>
+        <v>0.64</v>
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr">
@@ -1330,7 +1330,7 @@
       </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J12" s="4" t="inlineStr">
@@ -1348,24 +1348,24 @@
           <t>Sweet Spot</t>
         </is>
       </c>
-      <c r="M12" s="7" t="n">
+      <c r="M12" s="5" t="n">
         <v>8</v>
       </c>
       <c r="N12" s="4" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:BHEL</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:UNOMINDA</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>TORNTPHARM</t>
+          <t>ZYDUSLIFE</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>Torrent Pharmaceuticals</t>
+          <t>Zydus Lifesciences</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
@@ -1374,13 +1374,13 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>4946.5</v>
+        <v>1161.6</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>53.9</v>
+        <v>44.4</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>0.39</v>
+        <v>0.6</v>
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
@@ -1394,7 +1394,7 @@
       </c>
       <c r="I13" s="6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J13" s="6" t="inlineStr">
@@ -1412,39 +1412,39 @@
           <t>Sweet Spot</t>
         </is>
       </c>
-      <c r="M13" s="7" t="n">
+      <c r="M13" s="5" t="n">
         <v>8</v>
       </c>
       <c r="N13" s="6" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:TORNTPHARM</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:ZYDUSLIFE</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>JINDALSTEL</t>
+          <t>BOSCHLTD</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Jindal Steel &amp; Power</t>
+          <t>Bosch India</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>Metals &amp; Mining</t>
+          <t>Capital Goods</t>
         </is>
       </c>
       <c r="D14" s="4" t="n">
-        <v>1158.3</v>
+        <v>48835</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>67.40000000000001</v>
+        <v>79.2</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>0.36</v>
+        <v>0.59</v>
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
@@ -1453,7 +1453,7 @@
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I14" s="4" t="inlineStr">
@@ -1463,12 +1463,12 @@
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L14" s="4" t="inlineStr">
@@ -1476,12 +1476,12 @@
           <t>Sweet Spot</t>
         </is>
       </c>
-      <c r="M14" s="7" t="n">
+      <c r="M14" s="5" t="n">
         <v>8</v>
       </c>
       <c r="N14" s="4" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:JINDALSTEL</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:BOSCHLTD</t>
         </is>
       </c>
     </row>
@@ -1502,13 +1502,13 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>85.84999999999999</v>
+        <v>86.06999999999999</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>51.4</v>
+        <v>52.2</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>0.35</v>
+        <v>0.58</v>
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
@@ -1540,7 +1540,7 @@
           <t>Sweet Spot</t>
         </is>
       </c>
-      <c r="M15" s="7" t="n">
+      <c r="M15" s="5" t="n">
         <v>8</v>
       </c>
       <c r="N15" s="6" t="inlineStr">
@@ -1552,27 +1552,27 @@
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>AUBANK</t>
+          <t>DLF</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>AU Small Finance Bank</t>
+          <t>DLF</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D16" s="4" t="n">
-        <v>1071.9</v>
+        <v>671.2</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>50.3</v>
+        <v>62.9</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>0.34</v>
+        <v>0.52</v>
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
@@ -1604,39 +1604,39 @@
           <t>Sweet Spot</t>
         </is>
       </c>
-      <c r="M16" s="7" t="n">
+      <c r="M16" s="5" t="n">
         <v>8</v>
       </c>
       <c r="N16" s="4" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:AUBANK</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:DLF</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>UNIONBANK</t>
+          <t>JINDALSTEL</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>Union Bank</t>
+          <t>Jindal Steel &amp; Power</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Metals &amp; Mining</t>
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>183.4</v>
+        <v>1160.7</v>
       </c>
       <c r="E17" s="6" t="n">
-        <v>51.7</v>
+        <v>68.2</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>0.33</v>
+        <v>0.52</v>
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
@@ -1650,7 +1650,7 @@
       </c>
       <c r="I17" s="6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J17" s="6" t="inlineStr">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="K17" s="6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L17" s="6" t="inlineStr">
@@ -1668,39 +1668,39 @@
           <t>Sweet Spot</t>
         </is>
       </c>
-      <c r="M17" s="7" t="n">
+      <c r="M17" s="5" t="n">
         <v>8</v>
       </c>
       <c r="N17" s="6" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:UNIONBANK</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:JINDALSTEL</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>DLF</t>
+          <t>GRASIM</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>DLF</t>
+          <t>Grasim Industries</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Cement</t>
         </is>
       </c>
       <c r="D18" s="4" t="n">
-        <v>670.85</v>
+        <v>3312.6</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>62.6</v>
+        <v>48.3</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>0.32</v>
+        <v>0.49</v>
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
@@ -1732,39 +1732,39 @@
           <t>Sweet Spot</t>
         </is>
       </c>
-      <c r="M18" s="7" t="n">
+      <c r="M18" s="5" t="n">
         <v>8</v>
       </c>
       <c r="N18" s="4" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:DLF</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:GRASIM</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>GRASIM</t>
+          <t>PNBHOUSING</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>Grasim Industries</t>
+          <t>PNB Housing Finance</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>Cement</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>3310.6</v>
+        <v>1153.4</v>
       </c>
       <c r="E19" s="6" t="n">
-        <v>47.9</v>
+        <v>54.2</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>0.32</v>
+        <v>0.48</v>
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
@@ -1796,12 +1796,12 @@
           <t>Sweet Spot</t>
         </is>
       </c>
-      <c r="M19" s="7" t="n">
+      <c r="M19" s="5" t="n">
         <v>8</v>
       </c>
       <c r="N19" s="6" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:GRASIM</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:PNBHOUSING</t>
         </is>
       </c>
     </row>
@@ -1828,7 +1828,7 @@
         <v>63.2</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>0.29</v>
+        <v>0.41</v>
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
           <t>Sweet Spot</t>
         </is>
       </c>
-      <c r="M20" s="7" t="n">
+      <c r="M20" s="5" t="n">
         <v>8</v>
       </c>
       <c r="N20" s="4" t="inlineStr">
@@ -1872,12 +1872,12 @@
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>PNBHOUSING</t>
+          <t>POLICYBZR</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>PNB Housing Finance</t>
+          <t>PB Fintech</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
@@ -1886,13 +1886,13 @@
         </is>
       </c>
       <c r="D21" s="6" t="n">
-        <v>1156</v>
+        <v>1820.1</v>
       </c>
       <c r="E21" s="6" t="n">
-        <v>55.3</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>0.24</v>
+        <v>0.35</v>
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
@@ -1901,7 +1901,7 @@
       </c>
       <c r="H21" s="6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I21" s="6" t="inlineStr">
@@ -1911,7 +1911,7 @@
       </c>
       <c r="J21" s="6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K21" s="6" t="inlineStr">
@@ -1924,12 +1924,12 @@
           <t>Sweet Spot</t>
         </is>
       </c>
-      <c r="M21" s="7" t="n">
+      <c r="M21" s="5" t="n">
         <v>8</v>
       </c>
       <c r="N21" s="6" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:PNBHOUSING</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:POLICYBZR</t>
         </is>
       </c>
     </row>
@@ -2093,41 +2093,41 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>DELHIVERY</t>
+          <t>CAMS</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Delhivery</t>
+          <t>CAMS</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>Logistics</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D2" s="4" t="n">
-        <v>465.25</v>
+        <v>783</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>461.98</v>
+        <v>775.5</v>
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>SMA 20</t>
+          <t>SMA 50</t>
         </is>
       </c>
       <c r="G2" s="4" t="n">
-        <v>0.71</v>
+        <v>0.97</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>4.4</v>
+        <v>5.4</v>
       </c>
       <c r="I2" s="4" t="n">
-        <v>50.6</v>
+        <v>56.5</v>
       </c>
       <c r="J2" s="4" t="n">
-        <v>7.1</v>
+        <v>6</v>
       </c>
       <c r="K2" s="4" t="inlineStr">
         <is>
@@ -2141,12 +2141,12 @@
       </c>
       <c r="M2" s="4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="N2" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O2" s="4" t="inlineStr">
@@ -2161,70 +2161,70 @@
       </c>
       <c r="Q2" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="R2" s="4" t="inlineStr">
         <is>
-          <t>₹457.36–471.22</t>
+          <t>₹767.74–791.01</t>
         </is>
       </c>
       <c r="S2" s="4" t="n">
-        <v>524</v>
+        <v>845.64</v>
       </c>
       <c r="T2" s="4" t="n">
-        <v>448.12</v>
+        <v>752.23</v>
       </c>
       <c r="U2" s="4" t="n">
-        <v>3.4</v>
+        <v>2.1</v>
       </c>
       <c r="V2" s="5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W2" s="4" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:DELHIVERY</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:CAMS</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
         <is>
-          <t>MANKIND</t>
+          <t>DELHIVERY</t>
         </is>
       </c>
       <c r="B3" s="6" t="inlineStr">
         <is>
-          <t>Mankind Pharma</t>
+          <t>Delhivery</t>
         </is>
       </c>
       <c r="C3" s="6" t="inlineStr">
         <is>
-          <t>Pharma</t>
+          <t>Logistics</t>
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>2371.1</v>
+        <v>464.45</v>
       </c>
       <c r="E3" s="6" t="n">
-        <v>2340.7</v>
+        <v>461.94</v>
       </c>
       <c r="F3" s="6" t="inlineStr">
         <is>
-          <t>Swing Low</t>
+          <t>SMA 20</t>
         </is>
       </c>
       <c r="G3" s="6" t="n">
-        <v>1.3</v>
+        <v>0.54</v>
       </c>
       <c r="H3" s="6" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="I3" s="6" t="n">
-        <v>40.8</v>
+        <v>50.1</v>
       </c>
       <c r="J3" s="6" t="n">
-        <v>3.6</v>
+        <v>7.1</v>
       </c>
       <c r="K3" s="6" t="inlineStr">
         <is>
@@ -2233,7 +2233,7 @@
       </c>
       <c r="L3" s="6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="M3" s="6" t="inlineStr">
@@ -2263,36 +2263,36 @@
       </c>
       <c r="R3" s="6" t="inlineStr">
         <is>
-          <t>₹2317.29–2387.51</t>
+          <t>₹457.32–471.18</t>
         </is>
       </c>
       <c r="S3" s="6" t="n">
-        <v>2642</v>
+        <v>524</v>
       </c>
       <c r="T3" s="6" t="n">
-        <v>2270.48</v>
+        <v>448.08</v>
       </c>
       <c r="U3" s="6" t="n">
-        <v>2.7</v>
+        <v>3.7</v>
       </c>
       <c r="V3" s="5" t="n">
         <v>8</v>
       </c>
       <c r="W3" s="6" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:MANKIND</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:DELHIVERY</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>TECHM</t>
+          <t>MPHASIS</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>Tech Mahindra</t>
+          <t>Mphasis</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -2301,27 +2301,27 @@
         </is>
       </c>
       <c r="D4" s="4" t="n">
-        <v>1618.7</v>
+        <v>2406.3</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>1615.65</v>
+        <v>2404.24</v>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>SMA 20</t>
+          <t>SMA 200</t>
         </is>
       </c>
       <c r="G4" s="4" t="n">
-        <v>0.19</v>
+        <v>0.09</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>3.7</v>
+        <v>5.9</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>55.7</v>
+        <v>48.5</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>4.9</v>
+        <v>4</v>
       </c>
       <c r="K4" s="4" t="inlineStr">
         <is>
@@ -2330,7 +2330,7 @@
       </c>
       <c r="L4" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="M4" s="4" t="inlineStr">
@@ -2345,7 +2345,7 @@
       </c>
       <c r="O4" s="4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="P4" s="4" t="inlineStr">
@@ -2360,36 +2360,36 @@
       </c>
       <c r="R4" s="4" t="inlineStr">
         <is>
-          <t>₹1599.49–1647.96</t>
+          <t>₹2380.19–2452.32</t>
         </is>
       </c>
       <c r="S4" s="4" t="n">
-        <v>1748.2</v>
+        <v>2598.8</v>
       </c>
       <c r="T4" s="4" t="n">
-        <v>1567.18</v>
+        <v>2332.11</v>
       </c>
       <c r="U4" s="4" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="V4" s="5" t="n">
         <v>8</v>
       </c>
       <c r="W4" s="4" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:TECHM</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:MPHASIS</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>CAMS</t>
+          <t>SBIN</t>
         </is>
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>CAMS</t>
+          <t>State Bank of India</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
@@ -2398,10 +2398,10 @@
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>777.3</v>
+        <v>1045.1</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>775.5</v>
+        <v>1042.93</v>
       </c>
       <c r="F5" s="6" t="inlineStr">
         <is>
@@ -2409,16 +2409,16 @@
         </is>
       </c>
       <c r="G5" s="6" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>6.1</v>
+        <v>7.1</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>54.5</v>
+        <v>48.3</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>5.8</v>
+        <v>3</v>
       </c>
       <c r="K5" s="6" t="inlineStr">
         <is>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="M5" s="6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N5" s="6" t="inlineStr">
@@ -2442,7 +2442,7 @@
       </c>
       <c r="O5" s="6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="P5" s="6" t="inlineStr">
@@ -2452,19 +2452,19 @@
       </c>
       <c r="Q5" s="6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="R5" s="6" t="inlineStr">
         <is>
-          <t>₹767.74–791.01</t>
+          <t>₹1032.5–1063.79</t>
         </is>
       </c>
       <c r="S5" s="6" t="n">
-        <v>839.48</v>
+        <v>1128.71</v>
       </c>
       <c r="T5" s="6" t="n">
-        <v>752.23</v>
+        <v>1011.65</v>
       </c>
       <c r="U5" s="6" t="n">
         <v>2.5</v>
@@ -2474,48 +2474,48 @@
       </c>
       <c r="W5" s="6" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:CAMS</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:SBIN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>MPHASIS</t>
+          <t>INDHOTEL</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Mphasis</t>
+          <t>Indian Hotels (Taj)</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D6" s="4" t="n">
-        <v>2418.4</v>
+        <v>716.25</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>2404.3</v>
+        <v>713.25</v>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>SMA 200</t>
+          <t>Swing Low</t>
         </is>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.59</v>
+        <v>0.42</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>5.4</v>
+        <v>4.9</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>49.9</v>
+        <v>44.4</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>4</v>
+        <v>4.9</v>
       </c>
       <c r="K6" s="4" t="inlineStr">
         <is>
@@ -2529,12 +2529,12 @@
       </c>
       <c r="M6" s="4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="N6" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O6" s="4" t="inlineStr">
@@ -2554,65 +2554,65 @@
       </c>
       <c r="R6" s="4" t="inlineStr">
         <is>
-          <t>₹2380.25–2452.38</t>
+          <t>₹706.12–727.51</t>
         </is>
       </c>
       <c r="S6" s="4" t="n">
-        <v>2611.87</v>
+        <v>773.55</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>2332.17</v>
+        <v>691.85</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="V6" s="5" t="n">
         <v>8</v>
       </c>
       <c r="W6" s="4" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:MPHASIS</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:INDHOTEL</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>INDIGO</t>
+          <t>TECHM</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Tech Mahindra</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>Aviation</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>5100.5</v>
+        <v>1625.8</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>5064.5</v>
+        <v>1616</v>
       </c>
       <c r="F7" s="6" t="inlineStr">
         <is>
-          <t>Swing Low</t>
+          <t>SMA 20</t>
         </is>
       </c>
       <c r="G7" s="6" t="n">
-        <v>0.71</v>
+        <v>0.61</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>7.4</v>
+        <v>3.3</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>42.3</v>
+        <v>57.5</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="K7" s="6" t="inlineStr">
         <is>
@@ -2621,7 +2621,7 @@
       </c>
       <c r="L7" s="6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="M7" s="6" t="inlineStr">
@@ -2636,7 +2636,7 @@
       </c>
       <c r="O7" s="6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P7" s="6" t="inlineStr">
@@ -2651,14 +2651,14 @@
       </c>
       <c r="R7" s="6" t="inlineStr">
         <is>
-          <t>₹5013.85–5165.79</t>
+          <t>₹1599.84–1648.32</t>
         </is>
       </c>
       <c r="S7" s="6" t="n">
-        <v>5508.54</v>
+        <v>1755.86</v>
       </c>
       <c r="T7" s="6" t="n">
-        <v>4912.56</v>
+        <v>1567.52</v>
       </c>
       <c r="U7" s="6" t="n">
         <v>2.2</v>
@@ -2668,31 +2668,31 @@
       </c>
       <c r="W7" s="6" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:INDIGO</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:TECHM</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>GAIL</t>
+          <t>INDIGO</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>GAIL India</t>
+          <t>IndiGo</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>Oil &amp; Gas</t>
+          <t>Aviation</t>
         </is>
       </c>
       <c r="D8" s="4" t="n">
-        <v>172.27</v>
+        <v>5101.5</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>170.7</v>
+        <v>5064.5</v>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
@@ -2700,16 +2700,16 @@
         </is>
       </c>
       <c r="G8" s="4" t="n">
-        <v>0.92</v>
+        <v>0.73</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>3.2</v>
+        <v>7.4</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>47.1</v>
+        <v>42.4</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>3.6</v>
+        <v>4.4</v>
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
@@ -2748,69 +2748,69 @@
       </c>
       <c r="R8" s="4" t="inlineStr">
         <is>
-          <t>₹168.99–174.11</t>
+          <t>₹5013.85–5165.79</t>
         </is>
       </c>
       <c r="S8" s="4" t="n">
-        <v>186.05</v>
+        <v>5509.62</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>165.58</v>
+        <v>4912.56</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="V8" s="5" t="n">
         <v>8</v>
       </c>
       <c r="W8" s="4" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:GAIL</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:INDIGO</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>INDIANB</t>
+          <t>NMDC</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>Indian Bank</t>
+          <t>NMDC</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Metals &amp; Mining</t>
         </is>
       </c>
       <c r="D9" s="6" t="n">
-        <v>870.7</v>
+        <v>86.06999999999999</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>862</v>
+        <v>85.38</v>
       </c>
       <c r="F9" s="6" t="inlineStr">
         <is>
-          <t>Swing Low</t>
+          <t>SMA 50</t>
         </is>
       </c>
       <c r="G9" s="6" t="n">
-        <v>1.01</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>51.2</v>
+        <v>52.7</v>
       </c>
       <c r="J9" s="6" t="n">
         <v>4.6</v>
       </c>
       <c r="K9" s="6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L9" s="6" t="inlineStr">
@@ -2830,7 +2830,7 @@
       </c>
       <c r="O9" s="6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P9" s="6" t="inlineStr">
@@ -2845,65 +2845,65 @@
       </c>
       <c r="R9" s="6" t="inlineStr">
         <is>
-          <t>₹853.38–879.24</t>
+          <t>₹84.52–87.09</t>
         </is>
       </c>
       <c r="S9" s="6" t="n">
-        <v>940.36</v>
+        <v>92.95999999999999</v>
       </c>
       <c r="T9" s="6" t="n">
-        <v>836.14</v>
+        <v>82.81999999999999</v>
       </c>
       <c r="U9" s="6" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="V9" s="5" t="n">
         <v>8</v>
       </c>
       <c r="W9" s="6" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:INDIANB</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:NMDC</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>M&amp;M</t>
+          <t>SONACOMS</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Mahindra &amp; Mahindra</t>
+          <t>Sona BLW</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>Automobile</t>
+          <t>Capital Goods</t>
         </is>
       </c>
       <c r="D10" s="4" t="n">
-        <v>3352</v>
+        <v>816.35</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>3314.41</v>
+        <v>809.01</v>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>SMA 200</t>
+          <t>SMA 20</t>
         </is>
       </c>
       <c r="G10" s="4" t="n">
-        <v>1.13</v>
+        <v>0.91</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>5.2</v>
+        <v>3.3</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>49.4</v>
+        <v>62.8</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>4.4</v>
+        <v>3.6</v>
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
@@ -2912,7 +2912,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="M10" s="4" t="inlineStr">
@@ -2927,7 +2927,7 @@
       </c>
       <c r="O10" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P10" s="4" t="inlineStr">
@@ -2942,65 +2942,65 @@
       </c>
       <c r="R10" s="4" t="inlineStr">
         <is>
-          <t>₹3281.27–3380.7</t>
+          <t>₹800.92–825.2</t>
         </is>
       </c>
       <c r="S10" s="4" t="n">
-        <v>3620.16</v>
+        <v>881.66</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>3214.98</v>
+        <v>784.74</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="V10" s="5" t="n">
         <v>8</v>
       </c>
       <c r="W10" s="4" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:M&amp;M</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:SONACOMS</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>OBEROIRLTY</t>
+          <t>M&amp;M</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>Oberoi Realty</t>
+          <t>Mahindra &amp; Mahindra</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Automobile</t>
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>1866.6</v>
+        <v>3346.3</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>1844.73</v>
+        <v>3314.39</v>
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
-          <t>SMA 50</t>
+          <t>SMA 200</t>
         </is>
       </c>
       <c r="G11" s="6" t="n">
-        <v>1.19</v>
+        <v>0.96</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>53</v>
+        <v>48.7</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>3.4</v>
+        <v>4.4</v>
       </c>
       <c r="K11" s="6" t="inlineStr">
         <is>
@@ -3039,65 +3039,65 @@
       </c>
       <c r="R11" s="6" t="inlineStr">
         <is>
-          <t>₹1826.29–1881.63</t>
+          <t>₹3281.24–3380.67</t>
         </is>
       </c>
       <c r="S11" s="6" t="n">
-        <v>2015.93</v>
+        <v>3614</v>
       </c>
       <c r="T11" s="6" t="n">
-        <v>1789.39</v>
+        <v>3214.95</v>
       </c>
       <c r="U11" s="6" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="V11" s="5" t="n">
         <v>8</v>
       </c>
       <c r="W11" s="6" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:OBEROIRLTY</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:M&amp;M</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>RBLBANK</t>
+          <t>GAIL</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>RBL Bank</t>
+          <t>GAIL India</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Oil &amp; Gas</t>
         </is>
       </c>
       <c r="D12" s="4" t="n">
-        <v>381.1</v>
+        <v>172.35</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>376.4</v>
+        <v>170.7</v>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>SMA 50</t>
+          <t>Swing Low</t>
         </is>
       </c>
       <c r="G12" s="4" t="n">
-        <v>1.25</v>
+        <v>0.97</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>50.1</v>
+        <v>47.3</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>2.9</v>
+        <v>3.6</v>
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
@@ -3136,48 +3136,48 @@
       </c>
       <c r="R12" s="4" t="inlineStr">
         <is>
-          <t>₹372.64–383.93</t>
+          <t>₹168.99–174.11</t>
         </is>
       </c>
       <c r="S12" s="4" t="n">
-        <v>411.59</v>
+        <v>186.14</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>365.11</v>
+        <v>165.58</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="V12" s="5" t="n">
         <v>8</v>
       </c>
       <c r="W12" s="4" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:RBLBANK</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:GAIL</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>PIDILITIND</t>
+          <t>OBEROIRLTY</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>Pidilite Industries</t>
+          <t>Oberoi Realty</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>1638.1</v>
+        <v>1867.4</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>1616.43</v>
+        <v>1844.78</v>
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
@@ -3185,16 +3185,16 @@
         </is>
       </c>
       <c r="G13" s="6" t="n">
-        <v>1.34</v>
+        <v>1.23</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>48.9</v>
+        <v>53.1</v>
       </c>
       <c r="J13" s="6" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="K13" s="6" t="inlineStr">
         <is>
@@ -3203,7 +3203,7 @@
       </c>
       <c r="L13" s="6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="M13" s="6" t="inlineStr">
@@ -3228,19 +3228,19 @@
       </c>
       <c r="Q13" s="6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="R13" s="6" t="inlineStr">
         <is>
-          <t>₹1600.26–1648.75</t>
+          <t>₹1826.33–1881.67</t>
         </is>
       </c>
       <c r="S13" s="6" t="n">
-        <v>1769.15</v>
+        <v>2016.79</v>
       </c>
       <c r="T13" s="6" t="n">
-        <v>1567.93</v>
+        <v>1789.43</v>
       </c>
       <c r="U13" s="6" t="n">
         <v>1.9</v>
@@ -3250,52 +3250,52 @@
       </c>
       <c r="W13" s="6" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:PIDILITIND</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:OBEROIRLTY</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>ASTRAL</t>
+          <t>RBLBANK</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Astral</t>
+          <t>RBL Bank</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D14" s="4" t="n">
-        <v>1544.6</v>
+        <v>381.15</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>1518.21</v>
+        <v>376.4</v>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>SMA 200</t>
+          <t>SMA 50</t>
         </is>
       </c>
       <c r="G14" s="4" t="n">
-        <v>1.74</v>
+        <v>1.26</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>60.8</v>
+        <v>50.1</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L14" s="4" t="inlineStr">
@@ -3315,7 +3315,7 @@
       </c>
       <c r="O14" s="4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="P14" s="4" t="inlineStr">
@@ -3325,70 +3325,70 @@
       </c>
       <c r="Q14" s="4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="R14" s="4" t="inlineStr">
         <is>
-          <t>₹1503.03–1548.58</t>
+          <t>₹372.64–383.93</t>
         </is>
       </c>
       <c r="S14" s="4" t="n">
-        <v>1668.17</v>
+        <v>411.64</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>1472.67</v>
+        <v>365.11</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="V14" s="5" t="n">
         <v>8</v>
       </c>
       <c r="W14" s="4" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:ASTRAL</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:RBLBANK</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>OIL</t>
+          <t>PIDILITIND</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>Oil India</t>
+          <t>Pidilite Industries</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>Oil &amp; Gas</t>
+          <t>Chemicals</t>
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>483.9</v>
+        <v>1637.6</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>472.3</v>
+        <v>1616.42</v>
       </c>
       <c r="F15" s="6" t="inlineStr">
         <is>
-          <t>SMA 20</t>
+          <t>SMA 50</t>
         </is>
       </c>
       <c r="G15" s="6" t="n">
-        <v>2.46</v>
+        <v>1.31</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>3.2</v>
+        <v>4.1</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>62.5</v>
+        <v>48.8</v>
       </c>
       <c r="J15" s="6" t="n">
-        <v>8.5</v>
+        <v>3.5</v>
       </c>
       <c r="K15" s="6" t="inlineStr">
         <is>
@@ -3397,7 +3397,7 @@
       </c>
       <c r="L15" s="6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="M15" s="6" t="inlineStr">
@@ -3412,7 +3412,7 @@
       </c>
       <c r="O15" s="6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="P15" s="6" t="inlineStr">
@@ -3427,69 +3427,69 @@
       </c>
       <c r="R15" s="6" t="inlineStr">
         <is>
-          <t>₹467.58–481.75</t>
+          <t>₹1600.25–1648.74</t>
         </is>
       </c>
       <c r="S15" s="6" t="n">
-        <v>522.61</v>
+        <v>1768.61</v>
       </c>
       <c r="T15" s="6" t="n">
-        <v>458.13</v>
+        <v>1567.92</v>
       </c>
       <c r="U15" s="6" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="V15" s="5" t="n">
         <v>8</v>
       </c>
       <c r="W15" s="6" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:OIL</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:PIDILITIND</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>ADANIGREEN</t>
+          <t>OIL</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Adani Green Energy</t>
+          <t>Oil India</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t>Oil &amp; Gas</t>
         </is>
       </c>
       <c r="D16" s="4" t="n">
-        <v>1297.3</v>
+        <v>483.3</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>1291.4</v>
+        <v>472.3</v>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>Swing Low</t>
+          <t>SMA 20</t>
         </is>
       </c>
       <c r="G16" s="4" t="n">
-        <v>0.46</v>
+        <v>2.33</v>
       </c>
       <c r="H16" s="4" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="I16" s="4" t="n">
+        <v>62.2</v>
+      </c>
+      <c r="J16" s="4" t="n">
         <v>8.5</v>
       </c>
-      <c r="I16" s="4" t="n">
-        <v>38.4</v>
-      </c>
-      <c r="J16" s="4" t="n">
-        <v>4.5</v>
-      </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L16" s="4" t="inlineStr">
@@ -3509,7 +3509,7 @@
       </c>
       <c r="O16" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P16" s="4" t="inlineStr">
@@ -3519,74 +3519,74 @@
       </c>
       <c r="Q16" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="R16" s="4" t="inlineStr">
         <is>
-          <t>₹1278.49–1317.23</t>
+          <t>₹467.58–481.75</t>
         </is>
       </c>
       <c r="S16" s="4" t="n">
-        <v>1631.5</v>
+        <v>521.96</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>1252.66</v>
+        <v>458.13</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>7.6</v>
+        <v>1.5</v>
       </c>
       <c r="V16" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W16" s="4" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:ADANIGREEN</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:OIL</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>BSE</t>
+          <t>PHOENIXLTD</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>BSE</t>
+          <t>Phoenix Mills</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>3315.1</v>
+        <v>1891.5</v>
       </c>
       <c r="E17" s="6" t="n">
-        <v>3266.93</v>
+        <v>1877.3</v>
       </c>
       <c r="F17" s="6" t="inlineStr">
         <is>
-          <t>SMA 200</t>
+          <t>Swing Low</t>
         </is>
       </c>
       <c r="G17" s="6" t="n">
-        <v>1.47</v>
+        <v>0.76</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>9.5</v>
+        <v>3.9</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>40.5</v>
+        <v>41.3</v>
       </c>
       <c r="J17" s="6" t="n">
         <v>3.8</v>
       </c>
       <c r="K17" s="6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L17" s="6" t="inlineStr">
@@ -3606,7 +3606,7 @@
       </c>
       <c r="O17" s="6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="P17" s="6" t="inlineStr">
@@ -3621,24 +3621,24 @@
       </c>
       <c r="R17" s="6" t="inlineStr">
         <is>
-          <t>₹3234.26–3332.27</t>
+          <t>₹1858.53–1914.85</t>
         </is>
       </c>
       <c r="S17" s="6" t="n">
-        <v>4208.81</v>
+        <v>2169.8</v>
       </c>
       <c r="T17" s="6" t="n">
-        <v>3168.92</v>
+        <v>1820.98</v>
       </c>
       <c r="U17" s="6" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="V17" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="V17" s="7" t="n">
         <v>7</v>
       </c>
       <c r="W17" s="6" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:BSE</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:PHOENIXLTD</t>
         </is>
       </c>
     </row>
@@ -3659,7 +3659,7 @@
         </is>
       </c>
       <c r="D18" s="4" t="n">
-        <v>2032.9</v>
+        <v>2040.6</v>
       </c>
       <c r="E18" s="4" t="n">
         <v>2028</v>
@@ -3670,13 +3670,13 @@
         </is>
       </c>
       <c r="G18" s="4" t="n">
-        <v>0.24</v>
+        <v>0.62</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>11.4</v>
+        <v>11.1</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>41.4</v>
+        <v>42.5</v>
       </c>
       <c r="J18" s="4" t="n">
         <v>2.3</v>
@@ -3728,9 +3728,9 @@
         <v>1967.16</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="V18" s="5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="V18" s="7" t="n">
         <v>7</v>
       </c>
       <c r="W18" s="4" t="inlineStr">
@@ -3742,50 +3742,50 @@
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>FORTIS</t>
+          <t>NESTLEIND</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>Fortis Healthcare</t>
+          <t>Nestle India</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Consumer Goods</t>
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>914.65</v>
+        <v>1448.4</v>
       </c>
       <c r="E19" s="6" t="n">
-        <v>913.24</v>
+        <v>1448.3</v>
       </c>
       <c r="F19" s="6" t="inlineStr">
         <is>
-          <t>SMA 200</t>
+          <t>SMA 50</t>
         </is>
       </c>
       <c r="G19" s="6" t="n">
-        <v>0.15</v>
+        <v>0.01</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>6.5</v>
+        <v>6.7</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>45.4</v>
+        <v>42.2</v>
       </c>
       <c r="J19" s="6" t="n">
-        <v>4.4</v>
+        <v>3.5</v>
       </c>
       <c r="K19" s="6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L19" s="6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="M19" s="6" t="inlineStr">
@@ -3815,65 +3815,65 @@
       </c>
       <c r="R19" s="6" t="inlineStr">
         <is>
-          <t>₹904.11–931.51</t>
+          <t>₹1433.82–1477.27</t>
         </is>
       </c>
       <c r="S19" s="6" t="n">
-        <v>1009.03</v>
+        <v>1564.27</v>
       </c>
       <c r="T19" s="6" t="n">
-        <v>885.84</v>
+        <v>1404.85</v>
       </c>
       <c r="U19" s="6" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="V19" s="5" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="V19" s="7" t="n">
         <v>7</v>
       </c>
       <c r="W19" s="6" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:FORTIS</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:NESTLEIND</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>NESTLEIND</t>
+          <t>ASHOKLEY</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>Nestle India</t>
+          <t>Ashok Leyland</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>Consumer Goods</t>
+          <t>Automobile</t>
         </is>
       </c>
       <c r="D20" s="4" t="n">
-        <v>1449.4</v>
+        <v>175.67</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>1448.3</v>
+        <v>175.34</v>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>SMA 50</t>
+          <t>SMA 20</t>
         </is>
       </c>
       <c r="G20" s="4" t="n">
-        <v>0.08</v>
+        <v>0.19</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>6.7</v>
+        <v>3.8</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>42.5</v>
+        <v>57.8</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>3.5</v>
+        <v>5.8</v>
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
@@ -3897,7 +3897,7 @@
       </c>
       <c r="O20" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P20" s="4" t="inlineStr">
@@ -3912,65 +3912,65 @@
       </c>
       <c r="R20" s="4" t="inlineStr">
         <is>
-          <t>₹1433.82–1477.27</t>
+          <t>₹173.58–178.84</t>
         </is>
       </c>
       <c r="S20" s="4" t="n">
-        <v>1565.35</v>
+        <v>189.72</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>1404.85</v>
+        <v>170.07</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="V20" s="5" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="V20" s="7" t="n">
         <v>7</v>
       </c>
       <c r="W20" s="4" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:NESTLEIND</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:ASHOKLEY</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>MOTHERSON</t>
+          <t>BAJAJFINSV</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>Motherson Sumi</t>
+          <t>Bajaj Finserv</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>Automobile</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D21" s="6" t="n">
-        <v>166.28</v>
+        <v>1989.8</v>
       </c>
       <c r="E21" s="6" t="n">
-        <v>165.87</v>
+        <v>1985</v>
       </c>
       <c r="F21" s="6" t="inlineStr">
         <is>
-          <t>SMA 20</t>
+          <t>Swing Low</t>
         </is>
       </c>
       <c r="G21" s="6" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>4</v>
+        <v>6.1</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>61</v>
+        <v>50.6</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="K21" s="6" t="inlineStr">
         <is>
@@ -4009,24 +4009,24 @@
       </c>
       <c r="R21" s="6" t="inlineStr">
         <is>
-          <t>₹164.21–169.18</t>
+          <t>₹1965.15–2024.7</t>
         </is>
       </c>
       <c r="S21" s="6" t="n">
-        <v>179.58</v>
+        <v>2148.98</v>
       </c>
       <c r="T21" s="6" t="n">
-        <v>160.89</v>
+        <v>1925.45</v>
       </c>
       <c r="U21" s="6" t="n">
         <v>2.5</v>
       </c>
-      <c r="V21" s="5" t="n">
+      <c r="V21" s="7" t="n">
         <v>7</v>
       </c>
       <c r="W21" s="6" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:MOTHERSON</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:BAJAJFINSV</t>
         </is>
       </c>
     </row>
@@ -4190,12 +4190,12 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>CHOLAFIN</t>
+          <t>BAJAJFINSV</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Cholamandalam Investment</t>
+          <t>Bajaj Finserv</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
@@ -4204,19 +4204,19 @@
         </is>
       </c>
       <c r="D2" s="4" t="n">
-        <v>1834</v>
+        <v>1989.8</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>1962.26</v>
+        <v>2129.09</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>6.99</v>
+        <v>7</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>2068.26</v>
+        <v>2244.29</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>1797.32</v>
+        <v>1950</v>
       </c>
       <c r="I2" s="4" t="n">
         <v>2</v>
@@ -4225,16 +4225,16 @@
         <v>22</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>2.99</v>
+        <v>2.15</v>
       </c>
       <c r="L2" s="4" t="n">
-        <v>5.73</v>
+        <v>6.01</v>
       </c>
       <c r="M2" s="4" t="n">
-        <v>0.8</v>
+        <v>0.49</v>
       </c>
       <c r="N2" s="4" t="n">
-        <v>46.9</v>
+        <v>50.6</v>
       </c>
       <c r="O2" s="4" t="inlineStr">
         <is>
@@ -4276,19 +4276,19 @@
       </c>
       <c r="W2" s="4" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:CHOLAFIN</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:BAJAJFINSV</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>CHOLAFIN</t>
         </is>
       </c>
       <c r="B3" s="6" t="inlineStr">
         <is>
-          <t>Punjab National Bank</t>
+          <t>Cholamandalam Investment</t>
         </is>
       </c>
       <c r="C3" s="6" t="inlineStr">
@@ -4297,37 +4297,37 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>114.5</v>
+        <v>1835.1</v>
       </c>
       <c r="E3" s="6" t="n">
-        <v>120.1</v>
+        <v>1962.26</v>
       </c>
       <c r="F3" s="6" t="n">
-        <v>4.89</v>
+        <v>6.93</v>
       </c>
       <c r="G3" s="6" t="n">
-        <v>126.37</v>
+        <v>2067.16</v>
       </c>
       <c r="H3" s="6" t="n">
-        <v>110.46</v>
+        <v>1798.4</v>
       </c>
       <c r="I3" s="6" t="n">
-        <v>3.5</v>
+        <v>2</v>
       </c>
       <c r="J3" s="6" t="n">
         <v>22</v>
       </c>
       <c r="K3" s="6" t="n">
-        <v>3.06</v>
+        <v>2.93</v>
       </c>
       <c r="L3" s="6" t="n">
-        <v>5.55</v>
+        <v>5.71</v>
       </c>
       <c r="M3" s="6" t="n">
-        <v>0.77</v>
+        <v>0.84</v>
       </c>
       <c r="N3" s="6" t="n">
-        <v>50.4</v>
+        <v>47</v>
       </c>
       <c r="O3" s="6" t="inlineStr">
         <is>
@@ -4369,7 +4369,7 @@
       </c>
       <c r="W3" s="6" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:PNB</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:CHOLAFIN</t>
         </is>
       </c>
     </row>
@@ -4390,13 +4390,13 @@
         </is>
       </c>
       <c r="D4" s="4" t="n">
-        <v>3352</v>
+        <v>3346.3</v>
       </c>
       <c r="E4" s="4" t="n">
         <v>3552.27</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>5.97</v>
+        <v>6.16</v>
       </c>
       <c r="G4" s="4" t="n">
         <v>3739.27</v>
@@ -4405,22 +4405,22 @@
         <v>3263.4</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="J4" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>3.37</v>
+        <v>3.38</v>
       </c>
       <c r="L4" s="4" t="n">
-        <v>5.35</v>
+        <v>5.4</v>
       </c>
       <c r="M4" s="4" t="n">
-        <v>0.72</v>
+        <v>0.79</v>
       </c>
       <c r="N4" s="4" t="n">
-        <v>49.4</v>
+        <v>48.7</v>
       </c>
       <c r="O4" s="4" t="inlineStr">
         <is>
@@ -4469,55 +4469,55 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>UNOMINDA</t>
+          <t>BAJFINANCE</t>
         </is>
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>UNO Minda</t>
+          <t>Bajaj Finance</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>Automobile</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>1290.3</v>
+        <v>1065.6</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>1304.79</v>
+        <v>1118.56</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>1.12</v>
+        <v>4.97</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>1368.09</v>
+        <v>1155.16</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>1202.46</v>
+        <v>1044.29</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>6.8</v>
+        <v>2</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>3.02</v>
+        <v>2.76</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>5.76</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>0.72</v>
+        <v>0.74</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>67.09999999999999</v>
+        <v>45.8</v>
       </c>
       <c r="O5" s="6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P5" s="6" t="inlineStr">
@@ -4532,7 +4532,7 @@
       </c>
       <c r="R5" s="6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="S5" s="6" t="inlineStr">
@@ -4555,58 +4555,58 @@
       </c>
       <c r="W5" s="6" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:UNOMINDA</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:BAJFINANCE</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>BAJAJFINSV</t>
+          <t>PIDILITIND</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Bajaj Finserv</t>
+          <t>Pidilite Industries</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Chemicals</t>
         </is>
       </c>
       <c r="D6" s="4" t="n">
-        <v>1978</v>
+        <v>1637.6</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>2129.09</v>
+        <v>1716.04</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>7.64</v>
+        <v>4.79</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>2237.09</v>
+        <v>1806.24</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>1938.44</v>
+        <v>1579.07</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>2</v>
+        <v>3.6</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>2.76</v>
+        <v>2.72</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>6.17</v>
+        <v>5.25</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>0.44</v>
+        <v>0.67</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>48</v>
+        <v>48.8</v>
       </c>
       <c r="O6" s="4" t="inlineStr">
         <is>
@@ -4615,7 +4615,7 @@
       </c>
       <c r="P6" s="4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Q6" s="4" t="inlineStr">
@@ -4644,23 +4644,23 @@
         </is>
       </c>
       <c r="V6" s="5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W6" s="4" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:BAJAJFINSV</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:PIDILITIND</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>EICHERMOT</t>
+          <t>BAJAJ-AUTO</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>Eicher Motors</t>
+          <t>Bajaj Auto</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
@@ -4669,37 +4669,37 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>7965</v>
+        <v>11995</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>8205.82</v>
+        <v>12100.2</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>3.02</v>
+        <v>0.88</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>8616.84</v>
+        <v>12757.2</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>7535.2</v>
+        <v>11111.24</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>5.4</v>
+        <v>7.4</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K7" s="6" t="n">
-        <v>1.69</v>
+        <v>3.23</v>
       </c>
       <c r="L7" s="6" t="n">
-        <v>2.18</v>
+        <v>3.63</v>
       </c>
       <c r="M7" s="6" t="n">
-        <v>0.84</v>
+        <v>0.95</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>53.3</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="O7" s="6" t="inlineStr">
         <is>
@@ -4718,7 +4718,7 @@
       </c>
       <c r="R7" s="6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="S7" s="6" t="inlineStr">
@@ -4741,58 +4741,58 @@
       </c>
       <c r="W7" s="6" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:EICHERMOT</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:BAJAJ-AUTO</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>PIDILITIND</t>
+          <t>RBLBANK</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Pidilite Industries</t>
+          <t>RBL Bank</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D8" s="4" t="n">
-        <v>1638.1</v>
+        <v>381.15</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>1716.04</v>
+        <v>396.47</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>4.76</v>
+        <v>4.02</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>1806.24</v>
+        <v>418.78</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>1579.07</v>
+        <v>362.79</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>3.6</v>
+        <v>4.8</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>2.72</v>
+        <v>2.98</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>5.24</v>
+        <v>4.05</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>0.58</v>
+        <v>0.66</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>48.9</v>
+        <v>50.1</v>
       </c>
       <c r="O8" s="4" t="inlineStr">
         <is>
@@ -4834,19 +4834,19 @@
       </c>
       <c r="W8" s="4" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:PIDILITIND</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:RBLBANK</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>BAJAJ-AUTO</t>
+          <t>TVSMOTOR</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>Bajaj Auto</t>
+          <t>TVS Motor</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
@@ -4855,37 +4855,37 @@
         </is>
       </c>
       <c r="D9" s="6" t="n">
-        <v>11998</v>
+        <v>4322.9</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>12100.2</v>
+        <v>4506.92</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>0.85</v>
+        <v>4.26</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>12760.2</v>
+        <v>4764.72</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>11111.24</v>
+        <v>4124.23</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>7.4</v>
+        <v>4.6</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="K9" s="6" t="n">
-        <v>3.26</v>
+        <v>3.7</v>
       </c>
       <c r="L9" s="6" t="n">
-        <v>3.64</v>
+        <v>4.28</v>
       </c>
       <c r="M9" s="6" t="n">
-        <v>0.88</v>
+        <v>1.25</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>66.5</v>
+        <v>55.4</v>
       </c>
       <c r="O9" s="6" t="inlineStr">
         <is>
@@ -4894,7 +4894,7 @@
       </c>
       <c r="P9" s="6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="Q9" s="6" t="inlineStr">
@@ -4904,7 +4904,7 @@
       </c>
       <c r="R9" s="6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="S9" s="6" t="inlineStr">
@@ -4927,67 +4927,67 @@
       </c>
       <c r="W9" s="6" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:BAJAJ-AUTO</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:TVSMOTOR</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>LT</t>
+          <t>TITAN</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Larsen &amp; Toubro</t>
+          <t>Titan Company</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Consumer Goods</t>
         </is>
       </c>
       <c r="D10" s="4" t="n">
-        <v>4002.5</v>
+        <v>5125.9</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>4145.93</v>
+        <v>5212.63</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>3.58</v>
+        <v>1.69</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>4333.53</v>
+        <v>5506.63</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>3852.77</v>
+        <v>4777.7</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>3.7</v>
+        <v>6.8</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>2.91</v>
+        <v>2.35</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>3.06</v>
+        <v>5.35</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0.8</v>
+        <v>0.61</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>47.1</v>
+        <v>65.5</v>
       </c>
       <c r="O10" s="4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="P10" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="Q10" s="4" t="inlineStr">
@@ -5020,58 +5020,58 @@
       </c>
       <c r="W10" s="4" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:LT</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:TITAN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>RBLBANK</t>
+          <t>SUNPHARMA</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>RBL Bank</t>
+          <t>Sun Pharma</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Pharma</t>
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>381.1</v>
+        <v>1928.2</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>396.47</v>
+        <v>2057.13</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>4.03</v>
+        <v>6.69</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>418.78</v>
+        <v>2172.53</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>362.79</v>
+        <v>1837.6</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="K11" s="6" t="n">
-        <v>2.99</v>
+        <v>2.75</v>
       </c>
       <c r="L11" s="6" t="n">
-        <v>4.05</v>
+        <v>4.83</v>
       </c>
       <c r="M11" s="6" t="n">
-        <v>0.64</v>
+        <v>0.7</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>50.1</v>
+        <v>52.2</v>
       </c>
       <c r="O11" s="6" t="inlineStr">
         <is>
@@ -5080,7 +5080,7 @@
       </c>
       <c r="P11" s="6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="Q11" s="6" t="inlineStr">
@@ -5095,7 +5095,7 @@
       </c>
       <c r="S11" s="6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="T11" s="6" t="inlineStr">
@@ -5113,58 +5113,58 @@
       </c>
       <c r="W11" s="6" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:RBLBANK</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:SUNPHARMA</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>TVSMOTOR</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>TVS Motor</t>
+          <t>Punjab National Bank</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>Automobile</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D12" s="4" t="n">
-        <v>4323</v>
+        <v>114.74</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>4506.92</v>
+        <v>120.1</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>4.25</v>
+        <v>4.67</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>4764.72</v>
+        <v>126.37</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>4124.23</v>
+        <v>110.46</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>4.6</v>
+        <v>3.7</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>3.7</v>
+        <v>2.84</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>4.28</v>
+        <v>5.52</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>1.21</v>
+        <v>0.82</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>55.4</v>
+        <v>51.3</v>
       </c>
       <c r="O12" s="4" t="inlineStr">
         <is>
@@ -5178,7 +5178,7 @@
       </c>
       <c r="Q12" s="4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="R12" s="4" t="inlineStr">
@@ -5206,67 +5206,67 @@
       </c>
       <c r="W12" s="4" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:TVSMOTOR</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:PNB</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>TITAN</t>
+          <t>SBIN</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>Titan Company</t>
+          <t>State Bank of India</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>Consumer Goods</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>5115.9</v>
+        <v>1045.1</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>5212.63</v>
+        <v>1130.12</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>1.89</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>5506.63</v>
+        <v>1187.82</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>4777.7</v>
+        <v>1018.71</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>6.6</v>
+        <v>2.5</v>
       </c>
       <c r="J13" s="6" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K13" s="6" t="n">
-        <v>2.36</v>
+        <v>1.29</v>
       </c>
       <c r="L13" s="6" t="n">
-        <v>5.32</v>
+        <v>6.15</v>
       </c>
       <c r="M13" s="6" t="n">
         <v>0.6</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>64.2</v>
+        <v>48.3</v>
       </c>
       <c r="O13" s="6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P13" s="6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Q13" s="6" t="inlineStr">
@@ -5299,62 +5299,62 @@
       </c>
       <c r="W13" s="6" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:TITAN</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:SBIN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>SUNPHARMA</t>
+          <t>SONACOMS</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Sun Pharma</t>
+          <t>Sona BLW</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>Pharma</t>
+          <t>Capital Goods</t>
         </is>
       </c>
       <c r="D14" s="4" t="n">
-        <v>1925.5</v>
+        <v>816.35</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>2057.13</v>
+        <v>848.22</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>6.84</v>
+        <v>3.9</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>2172.53</v>
+        <v>887.22</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>1837.6</v>
+        <v>769.3</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>4.6</v>
+        <v>5.8</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>2.62</v>
+        <v>3.55</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>4.82</v>
+        <v>5.49</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.61</v>
+        <v>0.7</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>51.5</v>
+        <v>62.8</v>
       </c>
       <c r="O14" s="4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="P14" s="4" t="inlineStr">
@@ -5374,7 +5374,7 @@
       </c>
       <c r="S14" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="T14" s="4" t="inlineStr">
@@ -5392,58 +5392,58 @@
       </c>
       <c r="W14" s="4" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:SUNPHARMA</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:SONACOMS</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>360ONE</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>ABB India</t>
+          <t>360 ONE WAM</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>7399</v>
+        <v>1175</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>7864.12</v>
+        <v>1229.01</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>6.29</v>
+        <v>4.6</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>8175.12</v>
+        <v>1291.21</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>7251.02</v>
+        <v>1124.84</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>2</v>
+        <v>4.3</v>
       </c>
       <c r="J15" s="6" t="n">
         <v>21</v>
       </c>
       <c r="K15" s="6" t="n">
-        <v>3.08</v>
+        <v>3.95</v>
       </c>
       <c r="L15" s="6" t="n">
-        <v>4.85</v>
+        <v>5.23</v>
       </c>
       <c r="M15" s="6" t="n">
-        <v>0.82</v>
+        <v>0.65</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>46.9</v>
+        <v>51.1</v>
       </c>
       <c r="O15" s="6" t="inlineStr">
         <is>
@@ -5485,58 +5485,58 @@
       </c>
       <c r="W15" s="6" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:ABB</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:360ONE</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>SONACOMS</t>
+          <t>UNOMINDA</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Sona BLW</t>
+          <t>UNO Minda</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Automobile</t>
         </is>
       </c>
       <c r="D16" s="4" t="n">
-        <v>819.1</v>
+        <v>1280.8</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>848.22</v>
+        <v>1304.79</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>3.56</v>
+        <v>1.87</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>887.22</v>
+        <v>1365.79</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>769.3</v>
+        <v>1202.46</v>
       </c>
       <c r="I16" s="4" t="n">
         <v>6.1</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>3.54</v>
+        <v>2.3</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>5.54</v>
+        <v>5.57</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.66</v>
+        <v>0.77</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>63.6</v>
+        <v>65</v>
       </c>
       <c r="O16" s="4" t="inlineStr">
         <is>
@@ -5578,19 +5578,19 @@
       </c>
       <c r="W16" s="4" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:SONACOMS</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:UNOMINDA</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>360ONE</t>
+          <t>PNBHOUSING</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>360 ONE WAM</t>
+          <t>PNB Housing Finance</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
@@ -5599,46 +5599,46 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>1170.8</v>
+        <v>1153.4</v>
       </c>
       <c r="E17" s="6" t="n">
-        <v>1229.01</v>
+        <v>1217.56</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>4.97</v>
+        <v>5.56</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>1291.21</v>
+        <v>1280.96</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>1124.84</v>
+        <v>1099.17</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>3.9</v>
+        <v>4.7</v>
       </c>
       <c r="J17" s="6" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="K17" s="6" t="n">
-        <v>3.96</v>
+        <v>3.4</v>
       </c>
       <c r="L17" s="6" t="n">
-        <v>5.27</v>
+        <v>8.06</v>
       </c>
       <c r="M17" s="6" t="n">
-        <v>0.55</v>
+        <v>0.54</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>50</v>
+        <v>54.8</v>
       </c>
       <c r="O17" s="6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="P17" s="6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="Q17" s="6" t="inlineStr">
@@ -5671,67 +5671,67 @@
       </c>
       <c r="W17" s="6" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:360ONE</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:PNBHOUSING</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>MPHASIS</t>
+          <t>MOTHERSON</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>Mphasis</t>
+          <t>Motherson Sumi</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>Automobile</t>
         </is>
       </c>
       <c r="D18" s="4" t="n">
-        <v>2418.4</v>
+        <v>165.06</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>2569.68</v>
+        <v>174.14</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>6.26</v>
+        <v>5.5</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>2714.68</v>
+        <v>179.54</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>2352</v>
+        <v>161.7</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>2.7</v>
+        <v>2</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>2.27</v>
+        <v>3.27</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>8.199999999999999</v>
+        <v>13.2</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>0.83</v>
+        <v>0.53</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>49.9</v>
+        <v>58.2</v>
       </c>
       <c r="O18" s="4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="P18" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="Q18" s="4" t="inlineStr">
@@ -5764,62 +5764,62 @@
       </c>
       <c r="W18" s="4" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:MPHASIS</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:MOTHERSON</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>PNBHOUSING</t>
+          <t>DLF</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>PNB Housing Finance</t>
+          <t>DLF</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>1156</v>
+        <v>671.2</v>
       </c>
       <c r="E19" s="6" t="n">
-        <v>1217.56</v>
+        <v>693.85</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>5.33</v>
+        <v>3.37</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>1280.96</v>
+        <v>732.75</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>1099.17</v>
+        <v>637.1</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="J19" s="6" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="K19" s="6" t="n">
-        <v>3.39</v>
+        <v>3.46</v>
       </c>
       <c r="L19" s="6" t="n">
-        <v>8.050000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="M19" s="6" t="n">
-        <v>0.5</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>55.7</v>
+        <v>53.3</v>
       </c>
       <c r="O19" s="6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P19" s="6" t="inlineStr">
@@ -5839,7 +5839,7 @@
       </c>
       <c r="S19" s="6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="T19" s="6" t="inlineStr">
@@ -5857,58 +5857,58 @@
       </c>
       <c r="W19" s="6" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:PNBHOUSING</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:DLF</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>BAJFINANCE</t>
+          <t>APOLLOHOSP</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>Bajaj Finance</t>
+          <t>Apollo Hospitals</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D20" s="4" t="n">
-        <v>1061.6</v>
+        <v>8836</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>1118.56</v>
+        <v>9084.67</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>5.37</v>
+        <v>2.81</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>1159.16</v>
+        <v>9560.620000000001</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>1040.37</v>
+        <v>8392.26</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>17</v>
+        <v>49</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>3.15</v>
+        <v>2.22</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>8.970000000000001</v>
+        <v>5.26</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.61</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>44.7</v>
+        <v>52.1</v>
       </c>
       <c r="O20" s="4" t="inlineStr">
         <is>
@@ -5922,7 +5922,7 @@
       </c>
       <c r="Q20" s="4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="R20" s="4" t="inlineStr">
@@ -5932,7 +5932,7 @@
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="T20" s="4" t="inlineStr">
@@ -5945,72 +5945,72 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="V20" s="5" t="n">
-        <v>8</v>
+      <c r="V20" s="7" t="n">
+        <v>7</v>
       </c>
       <c r="W20" s="4" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:BAJFINANCE</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:APOLLOHOSP</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>MOTHERSON</t>
+          <t>TORNTPHARM</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>Motherson Sumi</t>
+          <t>Torrent Pharmaceuticals</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>Automobile</t>
+          <t>Pharma</t>
         </is>
       </c>
       <c r="D21" s="6" t="n">
-        <v>166.28</v>
+        <v>4930</v>
       </c>
       <c r="E21" s="6" t="n">
-        <v>174.14</v>
+        <v>5276.25</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>4.73</v>
+        <v>7.02</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>179.54</v>
+        <v>5566.05</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>161.7</v>
+        <v>4736.34</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>2.8</v>
+        <v>3.9</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="K21" s="6" t="n">
-        <v>3.25</v>
+        <v>3.32</v>
       </c>
       <c r="L21" s="6" t="n">
-        <v>13.19</v>
+        <v>4.61</v>
       </c>
       <c r="M21" s="6" t="n">
-        <v>0.46</v>
+        <v>0.73</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>61</v>
+        <v>50.1</v>
       </c>
       <c r="O21" s="6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P21" s="6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Q21" s="6" t="inlineStr">
@@ -6038,12 +6038,12 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="V21" s="5" t="n">
-        <v>8</v>
+      <c r="V21" s="7" t="n">
+        <v>7</v>
       </c>
       <c r="W21" s="6" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:MOTHERSON</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:TORNTPHARM</t>
         </is>
       </c>
     </row>

--- a/Analysis/exports/screener_2026-08-31.xlsx
+++ b/Analysis/exports/screener_2026-08-31.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Probable Upside" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Support Entry" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Consolidation Breakout" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Probable Upside" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Support Entry" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Consolidation Breakout" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -507,7 +507,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-31 15:00</t>
+          <t>2026-08-31 15:18</t>
         </is>
       </c>
     </row>
@@ -670,13 +670,13 @@
         </is>
       </c>
       <c r="D2" s="4" t="n">
-        <v>1684.6</v>
+        <v>1680</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>56.1</v>
+        <v>55.2</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>1.77</v>
+        <v>1.95</v>
       </c>
       <c r="G2" s="4" t="inlineStr">
         <is>
@@ -734,13 +734,13 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>11995</v>
+        <v>11997</v>
       </c>
       <c r="E3" s="6" t="n">
-        <v>61.8</v>
+        <v>61.9</v>
       </c>
       <c r="F3" s="6" t="n">
-        <v>1.16</v>
+        <v>1.29</v>
       </c>
       <c r="G3" s="6" t="inlineStr">
         <is>
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="D4" s="4" t="n">
-        <v>339.3</v>
+        <v>341.9</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>63.9</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>0.71</v>
+        <v>0.85</v>
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
@@ -848,27 +848,27 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>AUBANK</t>
+          <t>ZYDUSLIFE</t>
         </is>
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>AU Small Finance Bank</t>
+          <t>Zydus Lifesciences</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Pharma</t>
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>1077.9</v>
+        <v>1165.9</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>52.1</v>
+        <v>45.1</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>0.53</v>
+        <v>0.68</v>
       </c>
       <c r="G5" s="6" t="inlineStr">
         <is>
@@ -882,12 +882,12 @@
       </c>
       <c r="I5" s="6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J5" s="6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K5" s="6" t="inlineStr">
@@ -905,34 +905,34 @@
       </c>
       <c r="N5" s="6" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:AUBANK</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:ZYDUSLIFE</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>SOLARINDS</t>
+          <t>GRASIM</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Solar Industries</t>
+          <t>Grasim Industries</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Cement</t>
         </is>
       </c>
       <c r="D6" s="4" t="n">
-        <v>20242</v>
+        <v>3318.5</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>67.09999999999999</v>
+        <v>49.3</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.49</v>
+        <v>0.66</v>
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
@@ -946,12 +946,12 @@
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K6" s="4" t="inlineStr">
@@ -969,34 +969,34 @@
       </c>
       <c r="N6" s="4" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:SOLARINDS</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:GRASIM</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>ATHERENERG</t>
+          <t>AUBANK</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>Ather Energy</t>
+          <t>AU Small Finance Bank</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>Automobile</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>1687.3</v>
+        <v>1081.2</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>67.2</v>
+        <v>53.1</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>2.7</v>
+        <v>0.6</v>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
@@ -1005,12 +1005,12 @@
       </c>
       <c r="H7" s="6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I7" s="6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J7" s="6" t="inlineStr">
@@ -1029,38 +1029,38 @@
         </is>
       </c>
       <c r="M7" s="5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N7" s="6" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:ATHERENERG</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:AUBANK</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>SOLARINDS</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Laurus Labs</t>
+          <t>Solar Industries</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>Pharma</t>
+          <t>Capital Goods</t>
         </is>
       </c>
       <c r="D8" s="4" t="n">
-        <v>1874.1</v>
+        <v>20158</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>52.2</v>
+        <v>65.8</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>2.51</v>
+        <v>0.59</v>
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
@@ -1093,38 +1093,38 @@
         </is>
       </c>
       <c r="M8" s="5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N8" s="4" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:LAURUSLABS</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:SOLARINDS</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>ICICIBANK</t>
+          <t>ATHERENERG</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>ICICI Bank</t>
+          <t>Ather Energy</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Automobile</t>
         </is>
       </c>
       <c r="D9" s="6" t="n">
-        <v>1442.8</v>
+        <v>1649</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>54.6</v>
+        <v>64.3</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>1.28</v>
+        <v>2.93</v>
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
@@ -1133,12 +1133,12 @@
       </c>
       <c r="H9" s="6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I9" s="6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J9" s="6" t="inlineStr">
@@ -1161,34 +1161,34 @@
       </c>
       <c r="N9" s="6" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:ICICIBANK</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:ATHERENERG</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>HYUNDAI</t>
+          <t>ICICIBANK</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Hyundai Motor India</t>
+          <t>ICICI Bank</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D10" s="4" t="n">
-        <v>2248.7</v>
+        <v>1443.3</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>59.5</v>
+        <v>54.8</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>0.78</v>
+        <v>1.44</v>
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
@@ -1202,12 +1202,12 @@
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K10" s="4" t="inlineStr">
@@ -1225,19 +1225,19 @@
       </c>
       <c r="N10" s="4" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:HYUNDAI</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:ICICIBANK</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>MCX</t>
+          <t>BHEL</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>MCX</t>
+          <t>BHEL</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
@@ -1246,22 +1246,22 @@
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>3340.1</v>
+        <v>432</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>76.40000000000001</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>0.68</v>
+        <v>0.93</v>
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H11" s="6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I11" s="6" t="inlineStr">
@@ -1289,34 +1289,34 @@
       </c>
       <c r="N11" s="6" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:MCX</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:BHEL</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>UNOMINDA</t>
+          <t>HYUNDAI</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>UNO Minda</t>
+          <t>Hyundai Motor India</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>Automobile</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D12" s="4" t="n">
-        <v>1280.8</v>
+        <v>2251.7</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>51.9</v>
+        <v>60.2</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>0.64</v>
+        <v>0.86</v>
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
@@ -1330,7 +1330,7 @@
       </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J12" s="4" t="inlineStr">
@@ -1353,38 +1353,38 @@
       </c>
       <c r="N12" s="4" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:UNOMINDA</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:HYUNDAI</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>ZYDUSLIFE</t>
+          <t>APOLLOHOSP</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>Zydus Lifesciences</t>
+          <t>Apollo Hospitals</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>Pharma</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>1161.6</v>
+        <v>8849.5</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>44.4</v>
+        <v>54.9</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>0.6</v>
+        <v>0.82</v>
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H13" s="6" t="inlineStr">
@@ -1399,7 +1399,7 @@
       </c>
       <c r="J13" s="6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K13" s="6" t="inlineStr">
@@ -1417,34 +1417,34 @@
       </c>
       <c r="N13" s="6" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:ZYDUSLIFE</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:APOLLOHOSP</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>BOSCHLTD</t>
+          <t>UNOMINDA</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Bosch India</t>
+          <t>UNO Minda</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Automobile</t>
         </is>
       </c>
       <c r="D14" s="4" t="n">
-        <v>48835</v>
+        <v>1280</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>79.2</v>
+        <v>51.7</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>0.59</v>
+        <v>0.73</v>
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
@@ -1453,12 +1453,12 @@
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J14" s="4" t="inlineStr">
@@ -1481,34 +1481,34 @@
       </c>
       <c r="N14" s="4" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:BOSCHLTD</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:UNOMINDA</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>NMDC</t>
+          <t>DLF</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>NMDC</t>
+          <t>DLF</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>Metals &amp; Mining</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>86.06999999999999</v>
+        <v>668</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>52.2</v>
+        <v>60.5</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>0.58</v>
+        <v>0.66</v>
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
@@ -1545,34 +1545,34 @@
       </c>
       <c r="N15" s="6" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:NMDC</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:DLF</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>DLF</t>
+          <t>JINDALSTEL</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>DLF</t>
+          <t>Jindal Steel &amp; Power</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Metals &amp; Mining</t>
         </is>
       </c>
       <c r="D16" s="4" t="n">
-        <v>671.2</v>
+        <v>1158.7</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>62.9</v>
+        <v>67.5</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>0.52</v>
+        <v>0.58</v>
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J16" s="4" t="inlineStr">
@@ -1596,7 +1596,7 @@
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L16" s="4" t="inlineStr">
@@ -1609,34 +1609,34 @@
       </c>
       <c r="N16" s="4" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:DLF</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:JINDALSTEL</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>JINDALSTEL</t>
+          <t>PNBHOUSING</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>Jindal Steel &amp; Power</t>
+          <t>PNB Housing Finance</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>Metals &amp; Mining</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>1160.7</v>
+        <v>1145.4</v>
       </c>
       <c r="E17" s="6" t="n">
-        <v>68.2</v>
+        <v>51.2</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>0.52</v>
+        <v>0.58</v>
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
@@ -1650,7 +1650,7 @@
       </c>
       <c r="I17" s="6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J17" s="6" t="inlineStr">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="K17" s="6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L17" s="6" t="inlineStr">
@@ -1673,34 +1673,34 @@
       </c>
       <c r="N17" s="6" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:JINDALSTEL</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:PNBHOUSING</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>GRASIM</t>
+          <t>POLICYBZR</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>Grasim Industries</t>
+          <t>PB Fintech</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>Cement</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D18" s="4" t="n">
-        <v>3312.6</v>
+        <v>1820</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>48.3</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>0.49</v>
+        <v>0.55</v>
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
@@ -1709,7 +1709,7 @@
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I18" s="4" t="inlineStr">
@@ -1719,7 +1719,7 @@
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K18" s="4" t="inlineStr">
@@ -1737,34 +1737,34 @@
       </c>
       <c r="N18" s="4" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:GRASIM</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:POLICYBZR</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>PNBHOUSING</t>
+          <t>PAYTM</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>PNB Housing Finance</t>
+          <t>Paytm</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Fintech</t>
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>1153.4</v>
+        <v>1678.2</v>
       </c>
       <c r="E19" s="6" t="n">
-        <v>54.2</v>
+        <v>59.6</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>0.48</v>
+        <v>0.46</v>
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="H19" s="6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I19" s="6" t="inlineStr">
@@ -1783,7 +1783,7 @@
       </c>
       <c r="J19" s="6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K19" s="6" t="inlineStr">
@@ -1801,7 +1801,7 @@
       </c>
       <c r="N19" s="6" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:PNBHOUSING</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:PAYTM</t>
         </is>
       </c>
     </row>
@@ -1822,13 +1822,13 @@
         </is>
       </c>
       <c r="D20" s="4" t="n">
-        <v>14700</v>
+        <v>14688</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>63.2</v>
+        <v>63</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>0.41</v>
+        <v>0.45</v>
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
@@ -1872,27 +1872,27 @@
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>POLICYBZR</t>
+          <t>TITAN</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>PB Fintech</t>
+          <t>Titan Company</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Consumer Goods</t>
         </is>
       </c>
       <c r="D21" s="6" t="n">
-        <v>1820.1</v>
+        <v>5130</v>
       </c>
       <c r="E21" s="6" t="n">
-        <v>71.59999999999999</v>
+        <v>50.3</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
@@ -1901,7 +1901,7 @@
       </c>
       <c r="H21" s="6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I21" s="6" t="inlineStr">
@@ -1911,7 +1911,7 @@
       </c>
       <c r="J21" s="6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K21" s="6" t="inlineStr">
@@ -1929,7 +1929,7 @@
       </c>
       <c r="N21" s="6" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:POLICYBZR</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:TITAN</t>
         </is>
       </c>
     </row>
@@ -2093,41 +2093,41 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>CAMS</t>
+          <t>INDHOTEL</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>CAMS</t>
+          <t>Indian Hotels (Taj)</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D2" s="4" t="n">
-        <v>783</v>
+        <v>715.45</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>775.5</v>
+        <v>713.25</v>
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>SMA 50</t>
+          <t>Swing Low</t>
         </is>
       </c>
       <c r="G2" s="4" t="n">
-        <v>0.97</v>
+        <v>0.31</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>5.4</v>
+        <v>5</v>
       </c>
       <c r="I2" s="4" t="n">
-        <v>56.5</v>
+        <v>43.8</v>
       </c>
       <c r="J2" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K2" s="4" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
       </c>
       <c r="O2" s="4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="P2" s="4" t="inlineStr">
@@ -2166,65 +2166,65 @@
       </c>
       <c r="R2" s="4" t="inlineStr">
         <is>
-          <t>₹767.74–791.01</t>
+          <t>₹706.12–727.51</t>
         </is>
       </c>
       <c r="S2" s="4" t="n">
-        <v>845.64</v>
+        <v>772.6900000000001</v>
       </c>
       <c r="T2" s="4" t="n">
-        <v>752.23</v>
+        <v>691.85</v>
       </c>
       <c r="U2" s="4" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="V2" s="5" t="n">
         <v>9</v>
       </c>
       <c r="W2" s="4" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:CAMS</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:INDHOTEL</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
         <is>
-          <t>DELHIVERY</t>
+          <t>CAMS</t>
         </is>
       </c>
       <c r="B3" s="6" t="inlineStr">
         <is>
-          <t>Delhivery</t>
+          <t>CAMS</t>
         </is>
       </c>
       <c r="C3" s="6" t="inlineStr">
         <is>
-          <t>Logistics</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>464.45</v>
+        <v>784</v>
       </c>
       <c r="E3" s="6" t="n">
-        <v>461.94</v>
+        <v>775.5</v>
       </c>
       <c r="F3" s="6" t="inlineStr">
         <is>
-          <t>SMA 20</t>
+          <t>SMA 50</t>
         </is>
       </c>
       <c r="G3" s="6" t="n">
-        <v>0.54</v>
+        <v>1.1</v>
       </c>
       <c r="H3" s="6" t="n">
-        <v>4.6</v>
+        <v>5.3</v>
       </c>
       <c r="I3" s="6" t="n">
-        <v>50.1</v>
+        <v>56.8</v>
       </c>
       <c r="J3" s="6" t="n">
-        <v>7.1</v>
+        <v>6</v>
       </c>
       <c r="K3" s="6" t="inlineStr">
         <is>
@@ -2238,12 +2238,12 @@
       </c>
       <c r="M3" s="6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="N3" s="6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O3" s="6" t="inlineStr">
@@ -2258,53 +2258,53 @@
       </c>
       <c r="Q3" s="6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="R3" s="6" t="inlineStr">
         <is>
-          <t>₹457.32–471.18</t>
+          <t>₹767.74–791.01</t>
         </is>
       </c>
       <c r="S3" s="6" t="n">
-        <v>524</v>
+        <v>846.72</v>
       </c>
       <c r="T3" s="6" t="n">
-        <v>448.08</v>
+        <v>752.23</v>
       </c>
       <c r="U3" s="6" t="n">
-        <v>3.7</v>
+        <v>2</v>
       </c>
       <c r="V3" s="5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W3" s="6" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:DELHIVERY</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:CAMS</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>MPHASIS</t>
+          <t>M&amp;M</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>Mphasis</t>
+          <t>Mahindra &amp; Mahindra</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>Automobile</t>
         </is>
       </c>
       <c r="D4" s="4" t="n">
-        <v>2406.3</v>
+        <v>3354.7</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>2404.24</v>
+        <v>3314.43</v>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
@@ -2312,16 +2312,16 @@
         </is>
       </c>
       <c r="G4" s="4" t="n">
-        <v>0.09</v>
+        <v>1.22</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>5.9</v>
+        <v>5.1</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>48.5</v>
+        <v>49.7</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="K4" s="4" t="inlineStr">
         <is>
@@ -2355,41 +2355,41 @@
       </c>
       <c r="Q4" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="R4" s="4" t="inlineStr">
         <is>
-          <t>₹2380.19–2452.32</t>
+          <t>₹3281.28–3380.72</t>
         </is>
       </c>
       <c r="S4" s="4" t="n">
-        <v>2598.8</v>
+        <v>3623.08</v>
       </c>
       <c r="T4" s="4" t="n">
-        <v>2332.11</v>
+        <v>3214.99</v>
       </c>
       <c r="U4" s="4" t="n">
-        <v>2.6</v>
+        <v>1.9</v>
       </c>
       <c r="V4" s="5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W4" s="4" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:MPHASIS</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:M&amp;M</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>SBIN</t>
+          <t>YESBANK</t>
         </is>
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>State Bank of India</t>
+          <t>Yes Bank</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
@@ -2398,31 +2398,31 @@
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>1045.1</v>
+        <v>22.18</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>1042.93</v>
+        <v>22.18</v>
       </c>
       <c r="F5" s="6" t="inlineStr">
         <is>
-          <t>SMA 50</t>
+          <t>Swing Low</t>
         </is>
       </c>
       <c r="G5" s="6" t="n">
-        <v>0.21</v>
+        <v>0</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>7.1</v>
+        <v>4.2</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>48.3</v>
+        <v>36.8</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>3</v>
+        <v>3.7</v>
       </c>
       <c r="K5" s="6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L5" s="6" t="inlineStr">
@@ -2432,12 +2432,12 @@
       </c>
       <c r="M5" s="6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="N5" s="6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O5" s="6" t="inlineStr">
@@ -2452,70 +2452,70 @@
       </c>
       <c r="Q5" s="6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="R5" s="6" t="inlineStr">
         <is>
-          <t>₹1032.5–1063.79</t>
+          <t>₹21.96–22.62</t>
         </is>
       </c>
       <c r="S5" s="6" t="n">
-        <v>1128.71</v>
+        <v>25.78</v>
       </c>
       <c r="T5" s="6" t="n">
-        <v>1011.65</v>
+        <v>21.51</v>
       </c>
       <c r="U5" s="6" t="n">
-        <v>2.5</v>
+        <v>5.4</v>
       </c>
       <c r="V5" s="5" t="n">
         <v>8</v>
       </c>
       <c r="W5" s="6" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:SBIN</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:YESBANK</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>INDHOTEL</t>
+          <t>DELHIVERY</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Indian Hotels (Taj)</t>
+          <t>Delhivery</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Logistics</t>
         </is>
       </c>
       <c r="D6" s="4" t="n">
-        <v>716.25</v>
+        <v>464.95</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>713.25</v>
+        <v>461.97</v>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>Swing Low</t>
+          <t>SMA 20</t>
         </is>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.42</v>
+        <v>0.65</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>44.4</v>
+        <v>50.4</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>4.9</v>
+        <v>7.1</v>
       </c>
       <c r="K6" s="4" t="inlineStr">
         <is>
@@ -2529,17 +2529,17 @@
       </c>
       <c r="M6" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N6" s="4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="O6" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P6" s="4" t="inlineStr">
@@ -2554,162 +2554,162 @@
       </c>
       <c r="R6" s="4" t="inlineStr">
         <is>
-          <t>₹706.12–727.51</t>
+          <t>₹457.35–471.21</t>
         </is>
       </c>
       <c r="S6" s="4" t="n">
-        <v>773.55</v>
+        <v>524</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>691.85</v>
+        <v>448.11</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>2.4</v>
+        <v>3.5</v>
       </c>
       <c r="V6" s="5" t="n">
         <v>8</v>
       </c>
       <c r="W6" s="4" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:INDHOTEL</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:DELHIVERY</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>TECHM</t>
+          <t>BHARATFORG</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>Tech Mahindra</t>
+          <t>Bharat Forge</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>Capital Goods</t>
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>1625.8</v>
+        <v>2042.8</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>1616</v>
+        <v>2028</v>
       </c>
       <c r="F7" s="6" t="inlineStr">
         <is>
-          <t>SMA 20</t>
+          <t>Swing Low</t>
         </is>
       </c>
       <c r="G7" s="6" t="n">
-        <v>0.61</v>
+        <v>0.73</v>
       </c>
       <c r="H7" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>42.9</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="K7" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L7" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M7" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N7" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O7" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="P7" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q7" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R7" s="6" t="inlineStr">
+        <is>
+          <t>₹2007.72–2068.56</t>
+        </is>
+      </c>
+      <c r="S7" s="6" t="n">
+        <v>2295</v>
+      </c>
+      <c r="T7" s="6" t="n">
+        <v>1967.16</v>
+      </c>
+      <c r="U7" s="6" t="n">
         <v>3.3</v>
-      </c>
-      <c r="I7" s="6" t="n">
-        <v>57.5</v>
-      </c>
-      <c r="J7" s="6" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="K7" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L7" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M7" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="N7" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O7" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="P7" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Q7" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="R7" s="6" t="inlineStr">
-        <is>
-          <t>₹1599.84–1648.32</t>
-        </is>
-      </c>
-      <c r="S7" s="6" t="n">
-        <v>1755.86</v>
-      </c>
-      <c r="T7" s="6" t="n">
-        <v>1567.52</v>
-      </c>
-      <c r="U7" s="6" t="n">
-        <v>2.2</v>
       </c>
       <c r="V7" s="5" t="n">
         <v>8</v>
       </c>
       <c r="W7" s="6" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:TECHM</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:BHARATFORG</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>INDIGO</t>
+          <t>MOTHERSON</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Motherson Sumi</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>Aviation</t>
+          <t>Automobile</t>
         </is>
       </c>
       <c r="D8" s="4" t="n">
-        <v>5101.5</v>
+        <v>165.9</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>5064.5</v>
+        <v>165.85</v>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>Swing Low</t>
+          <t>SMA 20</t>
         </is>
       </c>
       <c r="G8" s="4" t="n">
-        <v>0.73</v>
+        <v>0.03</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>7.4</v>
+        <v>4.3</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>42.4</v>
+        <v>60.3</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>4.4</v>
+        <v>2.7</v>
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="L8" s="4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="M8" s="4" t="inlineStr">
@@ -2743,74 +2743,74 @@
       </c>
       <c r="Q8" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="R8" s="4" t="inlineStr">
         <is>
-          <t>₹5013.85–5165.79</t>
+          <t>₹164.19–169.16</t>
         </is>
       </c>
       <c r="S8" s="4" t="n">
-        <v>5509.62</v>
+        <v>179.17</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>4912.56</v>
+        <v>160.87</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>2.2</v>
+        <v>2.7</v>
       </c>
       <c r="V8" s="5" t="n">
         <v>8</v>
       </c>
       <c r="W8" s="4" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:INDIGO</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:MOTHERSON</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>NMDC</t>
+          <t>KFINTECH</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>NMDC</t>
+          <t>KFin Technologies</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>Metals &amp; Mining</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D9" s="6" t="n">
-        <v>86.06999999999999</v>
+        <v>951</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>85.38</v>
+        <v>950.41</v>
       </c>
       <c r="F9" s="6" t="inlineStr">
         <is>
-          <t>SMA 50</t>
+          <t>SMA 200</t>
         </is>
       </c>
       <c r="G9" s="6" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>52.7</v>
+        <v>52.9</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="K9" s="6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L9" s="6" t="inlineStr">
@@ -2830,63 +2830,63 @@
       </c>
       <c r="O9" s="6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="P9" s="6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Q9" s="6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="R9" s="6" t="inlineStr">
         <is>
-          <t>₹84.52–87.09</t>
+          <t>₹940.9–969.42</t>
         </is>
       </c>
       <c r="S9" s="6" t="n">
-        <v>92.95999999999999</v>
+        <v>1027.08</v>
       </c>
       <c r="T9" s="6" t="n">
-        <v>82.81999999999999</v>
+        <v>921.9</v>
       </c>
       <c r="U9" s="6" t="n">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
       <c r="V9" s="5" t="n">
         <v>8</v>
       </c>
       <c r="W9" s="6" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:NMDC</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:KFINTECH</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>SONACOMS</t>
+          <t>TECHM</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Sona BLW</t>
+          <t>Tech Mahindra</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="D10" s="4" t="n">
-        <v>816.35</v>
+        <v>1620</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>809.01</v>
+        <v>1615.71</v>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
@@ -2894,16 +2894,16 @@
         </is>
       </c>
       <c r="G10" s="4" t="n">
-        <v>0.91</v>
+        <v>0.27</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>62.8</v>
+        <v>56.1</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>3.6</v>
+        <v>4.9</v>
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
@@ -2942,48 +2942,48 @@
       </c>
       <c r="R10" s="4" t="inlineStr">
         <is>
-          <t>₹800.92–825.2</t>
+          <t>₹1599.55–1648.02</t>
         </is>
       </c>
       <c r="S10" s="4" t="n">
-        <v>881.66</v>
+        <v>1749.6</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>784.74</v>
+        <v>1567.24</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="V10" s="5" t="n">
         <v>8</v>
       </c>
       <c r="W10" s="4" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:SONACOMS</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:TECHM</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>M&amp;M</t>
+          <t>MPHASIS</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>Mahindra &amp; Mahindra</t>
+          <t>Mphasis</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>Automobile</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>3346.3</v>
+        <v>2415.1</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>3314.39</v>
+        <v>2404.28</v>
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
@@ -2991,16 +2991,16 @@
         </is>
       </c>
       <c r="G11" s="6" t="n">
-        <v>0.96</v>
+        <v>0.45</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>48.7</v>
+        <v>49.5</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="K11" s="6" t="inlineStr">
         <is>
@@ -3039,62 +3039,62 @@
       </c>
       <c r="R11" s="6" t="inlineStr">
         <is>
-          <t>₹3281.24–3380.67</t>
+          <t>₹2380.24–2452.37</t>
         </is>
       </c>
       <c r="S11" s="6" t="n">
-        <v>3614</v>
+        <v>2608.31</v>
       </c>
       <c r="T11" s="6" t="n">
-        <v>3214.95</v>
+        <v>2332.15</v>
       </c>
       <c r="U11" s="6" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="V11" s="5" t="n">
         <v>8</v>
       </c>
       <c r="W11" s="6" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:M&amp;M</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:MPHASIS</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>GAIL</t>
+          <t>SONACOMS</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>GAIL India</t>
+          <t>Sona BLW</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>Oil &amp; Gas</t>
+          <t>Capital Goods</t>
         </is>
       </c>
       <c r="D12" s="4" t="n">
-        <v>172.35</v>
+        <v>813.05</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>170.7</v>
+        <v>808.85</v>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>Swing Low</t>
+          <t>SMA 20</t>
         </is>
       </c>
       <c r="G12" s="4" t="n">
-        <v>0.97</v>
+        <v>0.52</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>47.3</v>
+        <v>61.5</v>
       </c>
       <c r="J12" s="4" t="n">
         <v>3.6</v>
@@ -3106,7 +3106,7 @@
       </c>
       <c r="L12" s="4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="M12" s="4" t="inlineStr">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="O12" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P12" s="4" t="inlineStr">
@@ -3136,65 +3136,65 @@
       </c>
       <c r="R12" s="4" t="inlineStr">
         <is>
-          <t>₹168.99–174.11</t>
+          <t>₹800.76–825.03</t>
         </is>
       </c>
       <c r="S12" s="4" t="n">
-        <v>186.14</v>
+        <v>878.09</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>165.58</v>
+        <v>784.58</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="V12" s="5" t="n">
         <v>8</v>
       </c>
       <c r="W12" s="4" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:GAIL</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:SONACOMS</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>OBEROIRLTY</t>
+          <t>IDFCFIRSTB</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>Oberoi Realty</t>
+          <t>IDFC First Bank</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>1867.4</v>
+        <v>84.3</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>1844.78</v>
+        <v>83.61</v>
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
-          <t>SMA 50</t>
+          <t>Swing Low</t>
         </is>
       </c>
       <c r="G13" s="6" t="n">
-        <v>1.23</v>
+        <v>0.83</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>4.8</v>
+        <v>3</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>53.1</v>
+        <v>51.2</v>
       </c>
       <c r="J13" s="6" t="n">
-        <v>3.4</v>
+        <v>4.9</v>
       </c>
       <c r="K13" s="6" t="inlineStr">
         <is>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="M13" s="6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="N13" s="6" t="inlineStr">
@@ -3228,53 +3228,53 @@
       </c>
       <c r="Q13" s="6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="R13" s="6" t="inlineStr">
         <is>
-          <t>₹1826.33–1881.67</t>
+          <t>₹82.77–85.28</t>
         </is>
       </c>
       <c r="S13" s="6" t="n">
-        <v>2016.79</v>
+        <v>91.04000000000001</v>
       </c>
       <c r="T13" s="6" t="n">
-        <v>1789.43</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="U13" s="6" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="V13" s="5" t="n">
         <v>8</v>
       </c>
       <c r="W13" s="6" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:OBEROIRLTY</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:IDFCFIRSTB</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>RBLBANK</t>
+          <t>OBEROIRLTY</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>RBL Bank</t>
+          <t>Oberoi Realty</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D14" s="4" t="n">
-        <v>381.15</v>
+        <v>1860.2</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>376.4</v>
+        <v>1844.41</v>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
@@ -3282,17 +3282,17 @@
         </is>
       </c>
       <c r="G14" s="4" t="n">
-        <v>1.26</v>
+        <v>0.86</v>
       </c>
       <c r="H14" s="4" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="I14" s="4" t="n">
+        <v>51.8</v>
+      </c>
+      <c r="J14" s="4" t="n">
         <v>3.4</v>
       </c>
-      <c r="I14" s="4" t="n">
-        <v>50.1</v>
-      </c>
-      <c r="J14" s="4" t="n">
-        <v>2.9</v>
-      </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -3330,65 +3330,65 @@
       </c>
       <c r="R14" s="4" t="inlineStr">
         <is>
-          <t>₹372.64–383.93</t>
+          <t>₹1825.97–1881.3</t>
         </is>
       </c>
       <c r="S14" s="4" t="n">
-        <v>411.64</v>
+        <v>2009.02</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>365.11</v>
+        <v>1789.08</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="V14" s="5" t="n">
         <v>8</v>
       </c>
       <c r="W14" s="4" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:RBLBANK</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:OBEROIRLTY</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>PIDILITIND</t>
+          <t>INDIGO</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>Pidilite Industries</t>
+          <t>IndiGo</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Aviation</t>
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>1637.6</v>
+        <v>5110</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>1616.42</v>
+        <v>5064.5</v>
       </c>
       <c r="F15" s="6" t="inlineStr">
         <is>
-          <t>SMA 50</t>
+          <t>Swing Low</t>
         </is>
       </c>
       <c r="G15" s="6" t="n">
-        <v>1.31</v>
+        <v>0.9</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>4.1</v>
+        <v>7.2</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>48.8</v>
+        <v>42.9</v>
       </c>
       <c r="J15" s="6" t="n">
-        <v>3.5</v>
+        <v>4.4</v>
       </c>
       <c r="K15" s="6" t="inlineStr">
         <is>
@@ -3397,7 +3397,7 @@
       </c>
       <c r="L15" s="6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="M15" s="6" t="inlineStr">
@@ -3422,41 +3422,41 @@
       </c>
       <c r="Q15" s="6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="R15" s="6" t="inlineStr">
         <is>
-          <t>₹1600.25–1648.74</t>
+          <t>₹5013.85–5165.79</t>
         </is>
       </c>
       <c r="S15" s="6" t="n">
-        <v>1768.61</v>
+        <v>5518.8</v>
       </c>
       <c r="T15" s="6" t="n">
-        <v>1567.92</v>
+        <v>4912.56</v>
       </c>
       <c r="U15" s="6" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="V15" s="5" t="n">
         <v>8</v>
       </c>
       <c r="W15" s="6" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:PIDILITIND</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:INDIGO</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>OIL</t>
+          <t>GAIL</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Oil India</t>
+          <t>GAIL India</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -3465,27 +3465,27 @@
         </is>
       </c>
       <c r="D16" s="4" t="n">
-        <v>483.3</v>
+        <v>172.32</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>472.3</v>
+        <v>170.7</v>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>SMA 20</t>
+          <t>Swing Low</t>
         </is>
       </c>
       <c r="G16" s="4" t="n">
-        <v>2.33</v>
+        <v>0.95</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>62.2</v>
+        <v>47.2</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>8.5</v>
+        <v>3.6</v>
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
@@ -3509,7 +3509,7 @@
       </c>
       <c r="O16" s="4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="P16" s="4" t="inlineStr">
@@ -3519,74 +3519,74 @@
       </c>
       <c r="Q16" s="4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="R16" s="4" t="inlineStr">
         <is>
-          <t>₹467.58–481.75</t>
+          <t>₹168.99–174.11</t>
         </is>
       </c>
       <c r="S16" s="4" t="n">
-        <v>521.96</v>
+        <v>186.11</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>458.13</v>
+        <v>165.58</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="V16" s="5" t="n">
         <v>8</v>
       </c>
       <c r="W16" s="4" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:OIL</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:GAIL</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>PHOENIXLTD</t>
+          <t>NMDC</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>Phoenix Mills</t>
+          <t>NMDC</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Metals &amp; Mining</t>
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>1891.5</v>
+        <v>86.20999999999999</v>
       </c>
       <c r="E17" s="6" t="n">
-        <v>1877.3</v>
+        <v>85.38</v>
       </c>
       <c r="F17" s="6" t="inlineStr">
         <is>
-          <t>Swing Low</t>
+          <t>SMA 50</t>
         </is>
       </c>
       <c r="G17" s="6" t="n">
-        <v>0.76</v>
+        <v>0.97</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>3.9</v>
+        <v>3.2</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>41.3</v>
+        <v>53.2</v>
       </c>
       <c r="J17" s="6" t="n">
-        <v>3.8</v>
+        <v>4.6</v>
       </c>
       <c r="K17" s="6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L17" s="6" t="inlineStr">
@@ -3606,12 +3606,12 @@
       </c>
       <c r="O17" s="6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P17" s="6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="Q17" s="6" t="inlineStr">
@@ -3621,65 +3621,65 @@
       </c>
       <c r="R17" s="6" t="inlineStr">
         <is>
-          <t>₹1858.53–1914.85</t>
+          <t>₹84.53–87.09</t>
         </is>
       </c>
       <c r="S17" s="6" t="n">
-        <v>2169.8</v>
+        <v>93.11</v>
       </c>
       <c r="T17" s="6" t="n">
-        <v>1820.98</v>
+        <v>82.81999999999999</v>
       </c>
       <c r="U17" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="V17" s="7" t="n">
-        <v>7</v>
+        <v>2.1</v>
+      </c>
+      <c r="V17" s="5" t="n">
+        <v>8</v>
       </c>
       <c r="W17" s="6" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:PHOENIXLTD</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:NMDC</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>BHARATFORG</t>
+          <t>PIDILITIND</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>Bharat Forge</t>
+          <t>Pidilite Industries</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Chemicals</t>
         </is>
       </c>
       <c r="D18" s="4" t="n">
-        <v>2040.6</v>
+        <v>1640</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>2028</v>
+        <v>1616.46</v>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>Swing Low</t>
+          <t>SMA 50</t>
         </is>
       </c>
       <c r="G18" s="4" t="n">
-        <v>0.62</v>
+        <v>1.46</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>11.1</v>
+        <v>4</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>42.5</v>
+        <v>49.4</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>2.3</v>
+        <v>3.5</v>
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
@@ -3713,53 +3713,53 @@
       </c>
       <c r="Q18" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="R18" s="4" t="inlineStr">
         <is>
-          <t>₹2007.72–2068.56</t>
+          <t>₹1600.3–1648.79</t>
         </is>
       </c>
       <c r="S18" s="4" t="n">
-        <v>2295</v>
+        <v>1771.2</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>1967.16</v>
+        <v>1567.97</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="V18" s="7" t="n">
-        <v>7</v>
+        <v>1.8</v>
+      </c>
+      <c r="V18" s="5" t="n">
+        <v>8</v>
       </c>
       <c r="W18" s="4" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:BHARATFORG</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:PIDILITIND</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>NESTLEIND</t>
+          <t>RBLBANK</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>Nestle India</t>
+          <t>RBL Bank</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>Consumer Goods</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>1448.4</v>
+        <v>381.9</v>
       </c>
       <c r="E19" s="6" t="n">
-        <v>1448.3</v>
+        <v>376.4</v>
       </c>
       <c r="F19" s="6" t="inlineStr">
         <is>
@@ -3767,16 +3767,16 @@
         </is>
       </c>
       <c r="G19" s="6" t="n">
-        <v>0.01</v>
+        <v>1.46</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>6.7</v>
+        <v>3.2</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>42.2</v>
+        <v>51</v>
       </c>
       <c r="J19" s="6" t="n">
-        <v>3.5</v>
+        <v>2.9</v>
       </c>
       <c r="K19" s="6" t="inlineStr">
         <is>
@@ -3785,7 +3785,7 @@
       </c>
       <c r="L19" s="6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="M19" s="6" t="inlineStr">
@@ -3815,65 +3815,65 @@
       </c>
       <c r="R19" s="6" t="inlineStr">
         <is>
-          <t>₹1433.82–1477.27</t>
+          <t>₹372.64–383.93</t>
         </is>
       </c>
       <c r="S19" s="6" t="n">
-        <v>1564.27</v>
+        <v>412.45</v>
       </c>
       <c r="T19" s="6" t="n">
-        <v>1404.85</v>
+        <v>365.11</v>
       </c>
       <c r="U19" s="6" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="V19" s="7" t="n">
-        <v>7</v>
+        <v>1.8</v>
+      </c>
+      <c r="V19" s="5" t="n">
+        <v>8</v>
       </c>
       <c r="W19" s="6" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:NESTLEIND</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:RBLBANK</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>ASHOKLEY</t>
+          <t>PHOENIXLTD</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>Ashok Leyland</t>
+          <t>Phoenix Mills</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>Automobile</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D20" s="4" t="n">
-        <v>175.67</v>
+        <v>1889.3</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>175.34</v>
+        <v>1877.3</v>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>SMA 20</t>
+          <t>Swing Low</t>
         </is>
       </c>
       <c r="G20" s="4" t="n">
-        <v>0.19</v>
+        <v>0.64</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>57.8</v>
+        <v>40.9</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>5.8</v>
+        <v>4.5</v>
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
@@ -3882,12 +3882,12 @@
       </c>
       <c r="L20" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="M20" s="4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="N20" s="4" t="inlineStr">
@@ -3897,7 +3897,7 @@
       </c>
       <c r="O20" s="4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="P20" s="4" t="inlineStr">
@@ -3912,24 +3912,24 @@
       </c>
       <c r="R20" s="4" t="inlineStr">
         <is>
-          <t>₹173.58–178.84</t>
+          <t>₹1858.53–1914.85</t>
         </is>
       </c>
       <c r="S20" s="4" t="n">
-        <v>189.72</v>
+        <v>2169.8</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>170.07</v>
+        <v>1820.98</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>2.5</v>
+        <v>4.1</v>
       </c>
       <c r="V20" s="7" t="n">
         <v>7</v>
       </c>
       <c r="W20" s="4" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:ASHOKLEY</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:PHOENIXLTD</t>
         </is>
       </c>
     </row>
@@ -3950,7 +3950,7 @@
         </is>
       </c>
       <c r="D21" s="6" t="n">
-        <v>1989.8</v>
+        <v>1985</v>
       </c>
       <c r="E21" s="6" t="n">
         <v>1985</v>
@@ -3961,16 +3961,16 @@
         </is>
       </c>
       <c r="G21" s="6" t="n">
-        <v>0.24</v>
+        <v>0</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>6.1</v>
+        <v>6.3</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>50.6</v>
+        <v>49.5</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="K21" s="6" t="inlineStr">
         <is>
@@ -4013,13 +4013,13 @@
         </is>
       </c>
       <c r="S21" s="6" t="n">
-        <v>2148.98</v>
+        <v>2143.8</v>
       </c>
       <c r="T21" s="6" t="n">
         <v>1925.45</v>
       </c>
       <c r="U21" s="6" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="V21" s="7" t="n">
         <v>7</v>
@@ -4190,51 +4190,51 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>BAJAJFINSV</t>
+          <t>M&amp;M</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Bajaj Finserv</t>
+          <t>Mahindra &amp; Mahindra</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Automobile</t>
         </is>
       </c>
       <c r="D2" s="4" t="n">
-        <v>1989.8</v>
+        <v>3354.7</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>2129.09</v>
+        <v>3552.27</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>7</v>
+        <v>5.89</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>2244.29</v>
+        <v>3739.27</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>1950</v>
+        <v>3263.4</v>
       </c>
       <c r="I2" s="4" t="n">
-        <v>2</v>
+        <v>2.7</v>
       </c>
       <c r="J2" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>2.15</v>
+        <v>3.37</v>
       </c>
       <c r="L2" s="4" t="n">
-        <v>6.01</v>
+        <v>5.33</v>
       </c>
       <c r="M2" s="4" t="n">
-        <v>0.49</v>
+        <v>0.82</v>
       </c>
       <c r="N2" s="4" t="n">
-        <v>50.6</v>
+        <v>49.7</v>
       </c>
       <c r="O2" s="4" t="inlineStr">
         <is>
@@ -4276,19 +4276,19 @@
       </c>
       <c r="W2" s="4" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:BAJAJFINSV</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:M&amp;M</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
         <is>
-          <t>CHOLAFIN</t>
+          <t>BAJAJFINSV</t>
         </is>
       </c>
       <c r="B3" s="6" t="inlineStr">
         <is>
-          <t>Cholamandalam Investment</t>
+          <t>Bajaj Finserv</t>
         </is>
       </c>
       <c r="C3" s="6" t="inlineStr">
@@ -4297,37 +4297,37 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>1835.1</v>
+        <v>1985</v>
       </c>
       <c r="E3" s="6" t="n">
-        <v>1962.26</v>
+        <v>2129.09</v>
       </c>
       <c r="F3" s="6" t="n">
-        <v>6.93</v>
+        <v>7.26</v>
       </c>
       <c r="G3" s="6" t="n">
-        <v>2067.16</v>
+        <v>2230.09</v>
       </c>
       <c r="H3" s="6" t="n">
-        <v>1798.4</v>
+        <v>1945.3</v>
       </c>
       <c r="I3" s="6" t="n">
         <v>2</v>
       </c>
       <c r="J3" s="6" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="K3" s="6" t="n">
-        <v>2.93</v>
+        <v>2.39</v>
       </c>
       <c r="L3" s="6" t="n">
-        <v>5.71</v>
+        <v>6.07</v>
       </c>
       <c r="M3" s="6" t="n">
-        <v>0.84</v>
+        <v>0.5</v>
       </c>
       <c r="N3" s="6" t="n">
-        <v>47</v>
+        <v>49.5</v>
       </c>
       <c r="O3" s="6" t="inlineStr">
         <is>
@@ -4369,58 +4369,58 @@
       </c>
       <c r="W3" s="6" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:CHOLAFIN</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:BAJAJFINSV</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>M&amp;M</t>
+          <t>BAJFINANCE</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>Mahindra &amp; Mahindra</t>
+          <t>Bajaj Finance</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>Automobile</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D4" s="4" t="n">
-        <v>3346.3</v>
+        <v>1064.4</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>3552.27</v>
+        <v>1118.56</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>6.16</v>
+        <v>5.09</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>3739.27</v>
+        <v>1156.36</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>3263.4</v>
+        <v>1043.11</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>3.38</v>
+        <v>2.87</v>
       </c>
       <c r="L4" s="4" t="n">
-        <v>5.4</v>
+        <v>8.9</v>
       </c>
       <c r="M4" s="4" t="n">
-        <v>0.79</v>
+        <v>0.76</v>
       </c>
       <c r="N4" s="4" t="n">
-        <v>48.7</v>
+        <v>45.5</v>
       </c>
       <c r="O4" s="4" t="inlineStr">
         <is>
@@ -4462,58 +4462,58 @@
       </c>
       <c r="W4" s="4" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:M&amp;M</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:BAJFINANCE</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>BAJFINANCE</t>
+          <t>PIDILITIND</t>
         </is>
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>Bajaj Finance</t>
+          <t>Pidilite Industries</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Chemicals</t>
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>1065.6</v>
+        <v>1640</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>1118.56</v>
+        <v>1716.04</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>4.97</v>
+        <v>4.64</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>1155.16</v>
+        <v>1806.24</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>1044.29</v>
+        <v>1579.07</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>2</v>
+        <v>3.7</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>2.76</v>
+        <v>2.71</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>8.869999999999999</v>
+        <v>5.21</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>0.74</v>
+        <v>0.72</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>45.8</v>
+        <v>49.4</v>
       </c>
       <c r="O5" s="6" t="inlineStr">
         <is>
@@ -4522,7 +4522,7 @@
       </c>
       <c r="P5" s="6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Q5" s="6" t="inlineStr">
@@ -4551,62 +4551,62 @@
         </is>
       </c>
       <c r="V5" s="5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W5" s="6" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:BAJFINANCE</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:PIDILITIND</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>PIDILITIND</t>
+          <t>BAJAJ-AUTO</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Pidilite Industries</t>
+          <t>Bajaj Auto</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Automobile</t>
         </is>
       </c>
       <c r="D6" s="4" t="n">
-        <v>1637.6</v>
+        <v>11997</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>1716.04</v>
+        <v>12100.2</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>4.79</v>
+        <v>0.86</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>1806.24</v>
+        <v>12759.2</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>1579.07</v>
+        <v>11111.24</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>3.6</v>
+        <v>7.4</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>2.72</v>
+        <v>3.25</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>5.25</v>
+        <v>3.63</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>0.67</v>
+        <v>0.97</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>48.8</v>
+        <v>66.5</v>
       </c>
       <c r="O6" s="4" t="inlineStr">
         <is>
@@ -4625,7 +4625,7 @@
       </c>
       <c r="R6" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="S6" s="4" t="inlineStr">
@@ -4648,58 +4648,58 @@
       </c>
       <c r="W6" s="4" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:PIDILITIND</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:BAJAJ-AUTO</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>BAJAJ-AUTO</t>
+          <t>RBLBANK</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>Bajaj Auto</t>
+          <t>RBL Bank</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>Automobile</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>11995</v>
+        <v>381.9</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>12100.2</v>
+        <v>396.47</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>0.88</v>
+        <v>3.82</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>12757.2</v>
+        <v>418.78</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>11111.24</v>
+        <v>362.79</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>7.4</v>
+        <v>5</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K7" s="6" t="n">
-        <v>3.23</v>
+        <v>2.88</v>
       </c>
       <c r="L7" s="6" t="n">
-        <v>3.63</v>
+        <v>4</v>
       </c>
       <c r="M7" s="6" t="n">
-        <v>0.95</v>
+        <v>0.71</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>66.40000000000001</v>
+        <v>51</v>
       </c>
       <c r="O7" s="6" t="inlineStr">
         <is>
@@ -4718,7 +4718,7 @@
       </c>
       <c r="R7" s="6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="S7" s="6" t="inlineStr">
@@ -4741,58 +4741,58 @@
       </c>
       <c r="W7" s="6" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:BAJAJ-AUTO</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:RBLBANK</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>RBLBANK</t>
+          <t>TVSMOTOR</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>RBL Bank</t>
+          <t>TVS Motor</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Automobile</t>
         </is>
       </c>
       <c r="D8" s="4" t="n">
-        <v>381.15</v>
+        <v>4322</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>396.47</v>
+        <v>4506.92</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>4.02</v>
+        <v>4.28</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>418.78</v>
+        <v>4764.72</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>362.79</v>
+        <v>4124.23</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>2.98</v>
+        <v>3.7</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>4.05</v>
+        <v>4.28</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>0.66</v>
+        <v>1.29</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>50.1</v>
+        <v>55.3</v>
       </c>
       <c r="O8" s="4" t="inlineStr">
         <is>
@@ -4801,7 +4801,7 @@
       </c>
       <c r="P8" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="Q8" s="4" t="inlineStr">
@@ -4834,62 +4834,62 @@
       </c>
       <c r="W8" s="4" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:RBLBANK</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:TVSMOTOR</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>TVSMOTOR</t>
+          <t>TITAN</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>TVS Motor</t>
+          <t>Titan Company</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>Automobile</t>
+          <t>Consumer Goods</t>
         </is>
       </c>
       <c r="D9" s="6" t="n">
-        <v>4322.9</v>
+        <v>5130</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>4506.92</v>
+        <v>5212.63</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>4.26</v>
+        <v>1.61</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>4764.72</v>
+        <v>5506.63</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>4124.23</v>
+        <v>4777.7</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>4.6</v>
+        <v>6.9</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K9" s="6" t="n">
-        <v>3.7</v>
+        <v>2.35</v>
       </c>
       <c r="L9" s="6" t="n">
-        <v>4.28</v>
+        <v>5.36</v>
       </c>
       <c r="M9" s="6" t="n">
-        <v>1.25</v>
+        <v>0.63</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>55.4</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="O9" s="6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="P9" s="6" t="inlineStr">
@@ -4927,62 +4927,62 @@
       </c>
       <c r="W9" s="6" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:TVSMOTOR</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:TITAN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>TITAN</t>
+          <t>SUNPHARMA</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Titan Company</t>
+          <t>Sun Pharma</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>Consumer Goods</t>
+          <t>Pharma</t>
         </is>
       </c>
       <c r="D10" s="4" t="n">
-        <v>5125.9</v>
+        <v>1925</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>5212.63</v>
+        <v>2057.13</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>1.69</v>
+        <v>6.86</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>5506.63</v>
+        <v>2172.53</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>4777.7</v>
+        <v>1837.6</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>6.8</v>
+        <v>4.5</v>
       </c>
       <c r="J10" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>2.35</v>
+        <v>2.59</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>5.35</v>
+        <v>4.82</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0.61</v>
+        <v>0.72</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>65.5</v>
+        <v>51.3</v>
       </c>
       <c r="O10" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P10" s="4" t="inlineStr">
@@ -5002,7 +5002,7 @@
       </c>
       <c r="S10" s="4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="T10" s="4" t="inlineStr">
@@ -5020,58 +5020,58 @@
       </c>
       <c r="W10" s="4" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:TITAN</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:SUNPHARMA</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>SUNPHARMA</t>
+          <t>CHOLAFIN</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>Sun Pharma</t>
+          <t>Cholamandalam Investment</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>Pharma</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>1928.2</v>
+        <v>1840.5</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>2057.13</v>
+        <v>1962.26</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>6.69</v>
+        <v>6.62</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>2172.53</v>
+        <v>2061.76</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>1837.6</v>
+        <v>1803.69</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>4.7</v>
+        <v>2</v>
       </c>
       <c r="J11" s="6" t="n">
         <v>22</v>
       </c>
       <c r="K11" s="6" t="n">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="L11" s="6" t="n">
-        <v>4.83</v>
+        <v>5.61</v>
       </c>
       <c r="M11" s="6" t="n">
-        <v>0.7</v>
+        <v>0.89</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>52.2</v>
+        <v>47.9</v>
       </c>
       <c r="O11" s="6" t="inlineStr">
         <is>
@@ -5095,7 +5095,7 @@
       </c>
       <c r="S11" s="6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="T11" s="6" t="inlineStr">
@@ -5113,7 +5113,7 @@
       </c>
       <c r="W11" s="6" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:SUNPHARMA</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:CHOLAFIN</t>
         </is>
       </c>
     </row>
@@ -5134,13 +5134,13 @@
         </is>
       </c>
       <c r="D12" s="4" t="n">
-        <v>114.74</v>
+        <v>114.56</v>
       </c>
       <c r="E12" s="4" t="n">
         <v>120.1</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>4.67</v>
+        <v>4.84</v>
       </c>
       <c r="G12" s="4" t="n">
         <v>126.37</v>
@@ -5149,22 +5149,22 @@
         <v>110.46</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="J12" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>2.84</v>
+        <v>3</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>5.52</v>
+        <v>5.54</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.82</v>
+        <v>0.85</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>51.3</v>
+        <v>50.6</v>
       </c>
       <c r="O12" s="4" t="inlineStr">
         <is>
@@ -5213,60 +5213,60 @@
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>SBIN</t>
+          <t>SONACOMS</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>State Bank of India</t>
+          <t>Sona BLW</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Capital Goods</t>
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>1045.1</v>
+        <v>813.05</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>1130.12</v>
+        <v>848.22</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>8.140000000000001</v>
+        <v>4.33</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>1187.82</v>
+        <v>887.22</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>1018.71</v>
+        <v>769.3</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>2.5</v>
+        <v>5.4</v>
       </c>
       <c r="J13" s="6" t="n">
         <v>21</v>
       </c>
       <c r="K13" s="6" t="n">
-        <v>1.29</v>
+        <v>3.57</v>
       </c>
       <c r="L13" s="6" t="n">
-        <v>6.15</v>
+        <v>5.45</v>
       </c>
       <c r="M13" s="6" t="n">
-        <v>0.6</v>
+        <v>0.72</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>48.3</v>
+        <v>61.5</v>
       </c>
       <c r="O13" s="6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="P13" s="6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="Q13" s="6" t="inlineStr">
@@ -5299,67 +5299,67 @@
       </c>
       <c r="W13" s="6" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:SBIN</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:SONACOMS</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>SONACOMS</t>
+          <t>360ONE</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Sona BLW</t>
+          <t>360 ONE WAM</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D14" s="4" t="n">
-        <v>816.35</v>
+        <v>1170</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>848.22</v>
+        <v>1229.01</v>
       </c>
       <c r="F14" s="4" t="n">
+        <v>5.04</v>
+      </c>
+      <c r="G14" s="4" t="n">
+        <v>1291.21</v>
+      </c>
+      <c r="H14" s="4" t="n">
+        <v>1124.84</v>
+      </c>
+      <c r="I14" s="4" t="n">
         <v>3.9</v>
-      </c>
-      <c r="G14" s="4" t="n">
-        <v>887.22</v>
-      </c>
-      <c r="H14" s="4" t="n">
-        <v>769.3</v>
-      </c>
-      <c r="I14" s="4" t="n">
-        <v>5.8</v>
       </c>
       <c r="J14" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>3.55</v>
+        <v>3.97</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>5.49</v>
+        <v>5.28</v>
       </c>
       <c r="M14" s="4" t="n">
         <v>0.7</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>62.8</v>
+        <v>49.8</v>
       </c>
       <c r="O14" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P14" s="4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Q14" s="4" t="inlineStr">
@@ -5392,67 +5392,67 @@
       </c>
       <c r="W14" s="4" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:SONACOMS</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:360ONE</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>360ONE</t>
+          <t>UNOMINDA</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>360 ONE WAM</t>
+          <t>UNO Minda</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Automobile</t>
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>1175</v>
+        <v>1280</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>1229.01</v>
+        <v>1304.79</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>4.6</v>
+        <v>1.94</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>1291.21</v>
+        <v>1365.79</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>1124.84</v>
+        <v>1202.46</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>4.3</v>
+        <v>6.1</v>
       </c>
       <c r="J15" s="6" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="K15" s="6" t="n">
-        <v>3.95</v>
+        <v>2.24</v>
       </c>
       <c r="L15" s="6" t="n">
-        <v>5.23</v>
+        <v>5.56</v>
       </c>
       <c r="M15" s="6" t="n">
-        <v>0.65</v>
+        <v>0.78</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>51.1</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="O15" s="6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="P15" s="6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="Q15" s="6" t="inlineStr">
@@ -5485,58 +5485,58 @@
       </c>
       <c r="W15" s="6" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:360ONE</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:UNOMINDA</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>UNOMINDA</t>
+          <t>PNBHOUSING</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>UNO Minda</t>
+          <t>PNB Housing Finance</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>Automobile</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D16" s="4" t="n">
-        <v>1280.8</v>
+        <v>1145.4</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>1304.79</v>
+        <v>1217.56</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>1.87</v>
+        <v>6.3</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>1365.79</v>
+        <v>1280.96</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>1202.46</v>
+        <v>1099.17</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>6.1</v>
+        <v>4</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>2.3</v>
+        <v>3.46</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>5.57</v>
+        <v>8.09</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.77</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>65</v>
+        <v>52.3</v>
       </c>
       <c r="O16" s="4" t="inlineStr">
         <is>
@@ -5578,58 +5578,58 @@
       </c>
       <c r="W16" s="4" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:UNOMINDA</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:PNBHOUSING</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>PNBHOUSING</t>
+          <t>MOTHERSON</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>PNB Housing Finance</t>
+          <t>Motherson Sumi</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Automobile</t>
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>1153.4</v>
+        <v>165.9</v>
       </c>
       <c r="E17" s="6" t="n">
-        <v>1217.56</v>
+        <v>174.14</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>5.56</v>
+        <v>4.97</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>1280.96</v>
+        <v>179.54</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>1099.17</v>
+        <v>161.7</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>4.7</v>
+        <v>2.5</v>
       </c>
       <c r="J17" s="6" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K17" s="6" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="L17" s="6" t="n">
-        <v>8.06</v>
+        <v>13.19</v>
       </c>
       <c r="M17" s="6" t="n">
-        <v>0.54</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>54.8</v>
+        <v>60.3</v>
       </c>
       <c r="O17" s="6" t="inlineStr">
         <is>
@@ -5671,62 +5671,62 @@
       </c>
       <c r="W17" s="6" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:PNBHOUSING</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:MOTHERSON</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>MOTHERSON</t>
+          <t>DLF</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>Motherson Sumi</t>
+          <t>DLF</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>Automobile</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D18" s="4" t="n">
-        <v>165.06</v>
+        <v>668</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>174.14</v>
+        <v>693.85</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>5.5</v>
+        <v>3.87</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>179.54</v>
+        <v>732.75</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>161.7</v>
+        <v>637.1</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>2</v>
+        <v>4.6</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>3.27</v>
+        <v>3.48</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>13.2</v>
+        <v>8.17</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>0.53</v>
+        <v>0.58</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>58.2</v>
+        <v>51.8</v>
       </c>
       <c r="O18" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P18" s="4" t="inlineStr">
@@ -5746,7 +5746,7 @@
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="T18" s="4" t="inlineStr">
@@ -5764,58 +5764,58 @@
       </c>
       <c r="W18" s="4" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:MOTHERSON</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:DLF</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>DLF</t>
+          <t>APOLLOHOSP</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>DLF</t>
+          <t>Apollo Hospitals</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>671.2</v>
+        <v>8849.5</v>
       </c>
       <c r="E19" s="6" t="n">
-        <v>693.85</v>
+        <v>9084.67</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>3.37</v>
+        <v>2.66</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>732.75</v>
+        <v>9560.620000000001</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>637.1</v>
+        <v>8392.26</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J19" s="6" t="n">
-        <v>16</v>
+        <v>49</v>
       </c>
       <c r="K19" s="6" t="n">
-        <v>3.46</v>
+        <v>2.21</v>
       </c>
       <c r="L19" s="6" t="n">
-        <v>8.199999999999999</v>
+        <v>5.26</v>
       </c>
       <c r="M19" s="6" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.64</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>53.3</v>
+        <v>52.7</v>
       </c>
       <c r="O19" s="6" t="inlineStr">
         <is>
@@ -5829,7 +5829,7 @@
       </c>
       <c r="Q19" s="6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="R19" s="6" t="inlineStr">
@@ -5852,63 +5852,63 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="V19" s="5" t="n">
-        <v>8</v>
+      <c r="V19" s="7" t="n">
+        <v>7</v>
       </c>
       <c r="W19" s="6" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:DLF</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:APOLLOHOSP</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>APOLLOHOSP</t>
+          <t>TORNTPHARM</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>Apollo Hospitals</t>
+          <t>Torrent Pharmaceuticals</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Pharma</t>
         </is>
       </c>
       <c r="D20" s="4" t="n">
-        <v>8836</v>
+        <v>4900.5</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>9084.67</v>
+        <v>5276.25</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>2.81</v>
+        <v>7.67</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>9560.620000000001</v>
+        <v>5566.05</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>8392.26</v>
+        <v>4736.34</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>5</v>
+        <v>3.3</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>2.22</v>
+        <v>3.34</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>5.26</v>
+        <v>4.66</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>0.61</v>
+        <v>0.78</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>52.1</v>
+        <v>48.4</v>
       </c>
       <c r="O20" s="4" t="inlineStr">
         <is>
@@ -5917,12 +5917,12 @@
       </c>
       <c r="P20" s="4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Q20" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="R20" s="4" t="inlineStr">
@@ -5932,7 +5932,7 @@
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="T20" s="4" t="inlineStr">
@@ -5950,58 +5950,58 @@
       </c>
       <c r="W20" s="4" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:APOLLOHOSP</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:TORNTPHARM</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>TORNTPHARM</t>
+          <t>LT</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>Torrent Pharmaceuticals</t>
+          <t>Larsen &amp; Toubro</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>Pharma</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D21" s="6" t="n">
-        <v>4930</v>
+        <v>4025</v>
       </c>
       <c r="E21" s="6" t="n">
-        <v>5276.25</v>
+        <v>4145.93</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>7.02</v>
+        <v>3</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>5566.05</v>
+        <v>4333.53</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>4736.34</v>
+        <v>3852.77</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="K21" s="6" t="n">
-        <v>3.32</v>
+        <v>2.34</v>
       </c>
       <c r="L21" s="6" t="n">
-        <v>4.61</v>
+        <v>2.91</v>
       </c>
       <c r="M21" s="6" t="n">
-        <v>0.73</v>
+        <v>0.88</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>50.1</v>
+        <v>49.7</v>
       </c>
       <c r="O21" s="6" t="inlineStr">
         <is>
@@ -6043,7 +6043,7 @@
       </c>
       <c r="W21" s="6" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:TORNTPHARM</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:LT</t>
         </is>
       </c>
     </row>

--- a/Analysis/exports/screener_2026-08-31.xlsx
+++ b/Analysis/exports/screener_2026-08-31.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Probable Upside" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Support Entry" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Consolidation Breakout" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Probable Upside" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Support Entry" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Consolidation Breakout" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -507,7 +507,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-31 15:18</t>
+          <t>2026-08-31 15:00</t>
         </is>
       </c>
     </row>
@@ -670,13 +670,13 @@
         </is>
       </c>
       <c r="D2" s="4" t="n">
-        <v>1680</v>
+        <v>1684.6</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>55.2</v>
+        <v>56.1</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>1.95</v>
+        <v>1.77</v>
       </c>
       <c r="G2" s="4" t="inlineStr">
         <is>
@@ -734,13 +734,13 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>11997</v>
+        <v>11995</v>
       </c>
       <c r="E3" s="6" t="n">
-        <v>61.9</v>
+        <v>61.8</v>
       </c>
       <c r="F3" s="6" t="n">
-        <v>1.29</v>
+        <v>1.16</v>
       </c>
       <c r="G3" s="6" t="inlineStr">
         <is>
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="D4" s="4" t="n">
-        <v>341.9</v>
+        <v>339.3</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>65.59999999999999</v>
+        <v>63.9</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>0.85</v>
+        <v>0.71</v>
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
@@ -848,27 +848,27 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>ZYDUSLIFE</t>
+          <t>AUBANK</t>
         </is>
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>Zydus Lifesciences</t>
+          <t>AU Small Finance Bank</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>Pharma</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>1165.9</v>
+        <v>1077.9</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>45.1</v>
+        <v>52.1</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>0.68</v>
+        <v>0.53</v>
       </c>
       <c r="G5" s="6" t="inlineStr">
         <is>
@@ -882,12 +882,12 @@
       </c>
       <c r="I5" s="6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J5" s="6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K5" s="6" t="inlineStr">
@@ -905,34 +905,34 @@
       </c>
       <c r="N5" s="6" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:ZYDUSLIFE</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:AUBANK</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>GRASIM</t>
+          <t>SOLARINDS</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Grasim Industries</t>
+          <t>Solar Industries</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>Cement</t>
+          <t>Capital Goods</t>
         </is>
       </c>
       <c r="D6" s="4" t="n">
-        <v>3318.5</v>
+        <v>20242</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>49.3</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.66</v>
+        <v>0.49</v>
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
@@ -946,12 +946,12 @@
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K6" s="4" t="inlineStr">
@@ -969,34 +969,34 @@
       </c>
       <c r="N6" s="4" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:GRASIM</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:SOLARINDS</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>AUBANK</t>
+          <t>ATHERENERG</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>AU Small Finance Bank</t>
+          <t>Ather Energy</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Automobile</t>
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>1081.2</v>
+        <v>1687.3</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>53.1</v>
+        <v>67.2</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>0.6</v>
+        <v>2.7</v>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
@@ -1005,12 +1005,12 @@
       </c>
       <c r="H7" s="6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I7" s="6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J7" s="6" t="inlineStr">
@@ -1029,38 +1029,38 @@
         </is>
       </c>
       <c r="M7" s="5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N7" s="6" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:AUBANK</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:ATHERENERG</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>SOLARINDS</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Solar Industries</t>
+          <t>Laurus Labs</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Pharma</t>
         </is>
       </c>
       <c r="D8" s="4" t="n">
-        <v>20158</v>
+        <v>1874.1</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>65.8</v>
+        <v>52.2</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.59</v>
+        <v>2.51</v>
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
@@ -1093,38 +1093,38 @@
         </is>
       </c>
       <c r="M8" s="5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N8" s="4" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:SOLARINDS</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:LAURUSLABS</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>ATHERENERG</t>
+          <t>ICICIBANK</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>Ather Energy</t>
+          <t>ICICI Bank</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>Automobile</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D9" s="6" t="n">
-        <v>1649</v>
+        <v>1442.8</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>64.3</v>
+        <v>54.6</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>2.93</v>
+        <v>1.28</v>
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
@@ -1133,12 +1133,12 @@
       </c>
       <c r="H9" s="6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I9" s="6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J9" s="6" t="inlineStr">
@@ -1161,34 +1161,34 @@
       </c>
       <c r="N9" s="6" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:ATHERENERG</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:ICICIBANK</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>ICICIBANK</t>
+          <t>HYUNDAI</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>ICICI Bank</t>
+          <t>Hyundai Motor India</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D10" s="4" t="n">
-        <v>1443.3</v>
+        <v>2248.7</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>54.8</v>
+        <v>59.5</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>1.44</v>
+        <v>0.78</v>
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
@@ -1202,12 +1202,12 @@
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K10" s="4" t="inlineStr">
@@ -1225,19 +1225,19 @@
       </c>
       <c r="N10" s="4" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:ICICIBANK</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:HYUNDAI</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>BHEL</t>
+          <t>MCX</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>BHEL</t>
+          <t>MCX</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
@@ -1246,22 +1246,22 @@
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>432</v>
+        <v>3340.1</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>66.59999999999999</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>0.93</v>
+        <v>0.68</v>
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H11" s="6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I11" s="6" t="inlineStr">
@@ -1289,34 +1289,34 @@
       </c>
       <c r="N11" s="6" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:BHEL</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:MCX</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>HYUNDAI</t>
+          <t>UNOMINDA</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Hyundai Motor India</t>
+          <t>UNO Minda</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Automobile</t>
         </is>
       </c>
       <c r="D12" s="4" t="n">
-        <v>2251.7</v>
+        <v>1280.8</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>60.2</v>
+        <v>51.9</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>0.86</v>
+        <v>0.64</v>
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
@@ -1330,7 +1330,7 @@
       </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J12" s="4" t="inlineStr">
@@ -1353,38 +1353,38 @@
       </c>
       <c r="N12" s="4" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:HYUNDAI</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:UNOMINDA</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>APOLLOHOSP</t>
+          <t>ZYDUSLIFE</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>Apollo Hospitals</t>
+          <t>Zydus Lifesciences</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Pharma</t>
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>8849.5</v>
+        <v>1161.6</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>54.9</v>
+        <v>44.4</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>0.82</v>
+        <v>0.6</v>
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H13" s="6" t="inlineStr">
@@ -1399,7 +1399,7 @@
       </c>
       <c r="J13" s="6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K13" s="6" t="inlineStr">
@@ -1417,34 +1417,34 @@
       </c>
       <c r="N13" s="6" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:APOLLOHOSP</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:ZYDUSLIFE</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>UNOMINDA</t>
+          <t>BOSCHLTD</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>UNO Minda</t>
+          <t>Bosch India</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>Automobile</t>
+          <t>Capital Goods</t>
         </is>
       </c>
       <c r="D14" s="4" t="n">
-        <v>1280</v>
+        <v>48835</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>51.7</v>
+        <v>79.2</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>0.73</v>
+        <v>0.59</v>
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
@@ -1453,12 +1453,12 @@
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J14" s="4" t="inlineStr">
@@ -1481,34 +1481,34 @@
       </c>
       <c r="N14" s="4" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:UNOMINDA</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:BOSCHLTD</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>DLF</t>
+          <t>NMDC</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>DLF</t>
+          <t>NMDC</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Metals &amp; Mining</t>
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>668</v>
+        <v>86.06999999999999</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>60.5</v>
+        <v>52.2</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>0.66</v>
+        <v>0.58</v>
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
@@ -1545,34 +1545,34 @@
       </c>
       <c r="N15" s="6" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:DLF</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:NMDC</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>JINDALSTEL</t>
+          <t>DLF</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Jindal Steel &amp; Power</t>
+          <t>DLF</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>Metals &amp; Mining</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D16" s="4" t="n">
-        <v>1158.7</v>
+        <v>671.2</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>67.5</v>
+        <v>62.9</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>0.58</v>
+        <v>0.52</v>
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J16" s="4" t="inlineStr">
@@ -1596,7 +1596,7 @@
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L16" s="4" t="inlineStr">
@@ -1609,34 +1609,34 @@
       </c>
       <c r="N16" s="4" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:JINDALSTEL</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:DLF</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>PNBHOUSING</t>
+          <t>JINDALSTEL</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>PNB Housing Finance</t>
+          <t>Jindal Steel &amp; Power</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Metals &amp; Mining</t>
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>1145.4</v>
+        <v>1160.7</v>
       </c>
       <c r="E17" s="6" t="n">
-        <v>51.2</v>
+        <v>68.2</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>0.58</v>
+        <v>0.52</v>
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
@@ -1650,7 +1650,7 @@
       </c>
       <c r="I17" s="6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J17" s="6" t="inlineStr">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="K17" s="6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L17" s="6" t="inlineStr">
@@ -1673,34 +1673,34 @@
       </c>
       <c r="N17" s="6" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:PNBHOUSING</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:JINDALSTEL</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>POLICYBZR</t>
+          <t>GRASIM</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>PB Fintech</t>
+          <t>Grasim Industries</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Cement</t>
         </is>
       </c>
       <c r="D18" s="4" t="n">
-        <v>1820</v>
+        <v>3312.6</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>71.59999999999999</v>
+        <v>48.3</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>0.55</v>
+        <v>0.49</v>
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
@@ -1709,7 +1709,7 @@
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I18" s="4" t="inlineStr">
@@ -1719,7 +1719,7 @@
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K18" s="4" t="inlineStr">
@@ -1737,34 +1737,34 @@
       </c>
       <c r="N18" s="4" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:POLICYBZR</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:GRASIM</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>PAYTM</t>
+          <t>PNBHOUSING</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>Paytm</t>
+          <t>PNB Housing Finance</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>Fintech</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>1678.2</v>
+        <v>1153.4</v>
       </c>
       <c r="E19" s="6" t="n">
-        <v>59.6</v>
+        <v>54.2</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>0.46</v>
+        <v>0.48</v>
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="H19" s="6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I19" s="6" t="inlineStr">
@@ -1783,7 +1783,7 @@
       </c>
       <c r="J19" s="6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K19" s="6" t="inlineStr">
@@ -1801,7 +1801,7 @@
       </c>
       <c r="N19" s="6" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:PAYTM</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:PNBHOUSING</t>
         </is>
       </c>
     </row>
@@ -1822,13 +1822,13 @@
         </is>
       </c>
       <c r="D20" s="4" t="n">
-        <v>14688</v>
+        <v>14700</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>63</v>
+        <v>63.2</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>0.45</v>
+        <v>0.41</v>
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
@@ -1872,27 +1872,27 @@
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>TITAN</t>
+          <t>POLICYBZR</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>Titan Company</t>
+          <t>PB Fintech</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>Consumer Goods</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D21" s="6" t="n">
-        <v>5130</v>
+        <v>1820.1</v>
       </c>
       <c r="E21" s="6" t="n">
-        <v>50.3</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>0.36</v>
+        <v>0.35</v>
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
@@ -1901,7 +1901,7 @@
       </c>
       <c r="H21" s="6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I21" s="6" t="inlineStr">
@@ -1911,7 +1911,7 @@
       </c>
       <c r="J21" s="6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K21" s="6" t="inlineStr">
@@ -1929,7 +1929,7 @@
       </c>
       <c r="N21" s="6" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:TITAN</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:POLICYBZR</t>
         </is>
       </c>
     </row>
@@ -2093,41 +2093,41 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>INDHOTEL</t>
+          <t>CAMS</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Indian Hotels (Taj)</t>
+          <t>CAMS</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D2" s="4" t="n">
-        <v>715.45</v>
+        <v>783</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>713.25</v>
+        <v>775.5</v>
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>Swing Low</t>
+          <t>SMA 50</t>
         </is>
       </c>
       <c r="G2" s="4" t="n">
-        <v>0.31</v>
+        <v>0.97</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="I2" s="4" t="n">
-        <v>43.8</v>
+        <v>56.5</v>
       </c>
       <c r="J2" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K2" s="4" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
       </c>
       <c r="O2" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P2" s="4" t="inlineStr">
@@ -2166,65 +2166,65 @@
       </c>
       <c r="R2" s="4" t="inlineStr">
         <is>
-          <t>₹706.12–727.51</t>
+          <t>₹767.74–791.01</t>
         </is>
       </c>
       <c r="S2" s="4" t="n">
-        <v>772.6900000000001</v>
+        <v>845.64</v>
       </c>
       <c r="T2" s="4" t="n">
-        <v>691.85</v>
+        <v>752.23</v>
       </c>
       <c r="U2" s="4" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="V2" s="5" t="n">
         <v>9</v>
       </c>
       <c r="W2" s="4" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:INDHOTEL</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:CAMS</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
         <is>
-          <t>CAMS</t>
+          <t>DELHIVERY</t>
         </is>
       </c>
       <c r="B3" s="6" t="inlineStr">
         <is>
-          <t>CAMS</t>
+          <t>Delhivery</t>
         </is>
       </c>
       <c r="C3" s="6" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Logistics</t>
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>784</v>
+        <v>464.45</v>
       </c>
       <c r="E3" s="6" t="n">
-        <v>775.5</v>
+        <v>461.94</v>
       </c>
       <c r="F3" s="6" t="inlineStr">
         <is>
-          <t>SMA 50</t>
+          <t>SMA 20</t>
         </is>
       </c>
       <c r="G3" s="6" t="n">
-        <v>1.1</v>
+        <v>0.54</v>
       </c>
       <c r="H3" s="6" t="n">
-        <v>5.3</v>
+        <v>4.6</v>
       </c>
       <c r="I3" s="6" t="n">
-        <v>56.8</v>
+        <v>50.1</v>
       </c>
       <c r="J3" s="6" t="n">
-        <v>6</v>
+        <v>7.1</v>
       </c>
       <c r="K3" s="6" t="inlineStr">
         <is>
@@ -2238,12 +2238,12 @@
       </c>
       <c r="M3" s="6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N3" s="6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="O3" s="6" t="inlineStr">
@@ -2258,53 +2258,53 @@
       </c>
       <c r="Q3" s="6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="R3" s="6" t="inlineStr">
         <is>
-          <t>₹767.74–791.01</t>
+          <t>₹457.32–471.18</t>
         </is>
       </c>
       <c r="S3" s="6" t="n">
-        <v>846.72</v>
+        <v>524</v>
       </c>
       <c r="T3" s="6" t="n">
-        <v>752.23</v>
+        <v>448.08</v>
       </c>
       <c r="U3" s="6" t="n">
-        <v>2</v>
+        <v>3.7</v>
       </c>
       <c r="V3" s="5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W3" s="6" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:CAMS</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:DELHIVERY</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>M&amp;M</t>
+          <t>MPHASIS</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>Mahindra &amp; Mahindra</t>
+          <t>Mphasis</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>Automobile</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="D4" s="4" t="n">
-        <v>3354.7</v>
+        <v>2406.3</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>3314.43</v>
+        <v>2404.24</v>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
@@ -2312,16 +2312,16 @@
         </is>
       </c>
       <c r="G4" s="4" t="n">
-        <v>1.22</v>
+        <v>0.09</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>5.1</v>
+        <v>5.9</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>49.7</v>
+        <v>48.5</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="K4" s="4" t="inlineStr">
         <is>
@@ -2355,41 +2355,41 @@
       </c>
       <c r="Q4" s="4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="R4" s="4" t="inlineStr">
         <is>
-          <t>₹3281.28–3380.72</t>
+          <t>₹2380.19–2452.32</t>
         </is>
       </c>
       <c r="S4" s="4" t="n">
-        <v>3623.08</v>
+        <v>2598.8</v>
       </c>
       <c r="T4" s="4" t="n">
-        <v>3214.99</v>
+        <v>2332.11</v>
       </c>
       <c r="U4" s="4" t="n">
-        <v>1.9</v>
+        <v>2.6</v>
       </c>
       <c r="V4" s="5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W4" s="4" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:M&amp;M</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:MPHASIS</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>YESBANK</t>
+          <t>SBIN</t>
         </is>
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>Yes Bank</t>
+          <t>State Bank of India</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
@@ -2398,31 +2398,31 @@
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>22.18</v>
+        <v>1045.1</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>22.18</v>
+        <v>1042.93</v>
       </c>
       <c r="F5" s="6" t="inlineStr">
         <is>
-          <t>Swing Low</t>
+          <t>SMA 50</t>
         </is>
       </c>
       <c r="G5" s="6" t="n">
-        <v>0</v>
+        <v>0.21</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>4.2</v>
+        <v>7.1</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>36.8</v>
+        <v>48.3</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>3.7</v>
+        <v>3</v>
       </c>
       <c r="K5" s="6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L5" s="6" t="inlineStr">
@@ -2432,12 +2432,12 @@
       </c>
       <c r="M5" s="6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N5" s="6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="O5" s="6" t="inlineStr">
@@ -2452,70 +2452,70 @@
       </c>
       <c r="Q5" s="6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="R5" s="6" t="inlineStr">
         <is>
-          <t>₹21.96–22.62</t>
+          <t>₹1032.5–1063.79</t>
         </is>
       </c>
       <c r="S5" s="6" t="n">
-        <v>25.78</v>
+        <v>1128.71</v>
       </c>
       <c r="T5" s="6" t="n">
-        <v>21.51</v>
+        <v>1011.65</v>
       </c>
       <c r="U5" s="6" t="n">
-        <v>5.4</v>
+        <v>2.5</v>
       </c>
       <c r="V5" s="5" t="n">
         <v>8</v>
       </c>
       <c r="W5" s="6" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:YESBANK</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:SBIN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>DELHIVERY</t>
+          <t>INDHOTEL</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Delhivery</t>
+          <t>Indian Hotels (Taj)</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>Logistics</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D6" s="4" t="n">
-        <v>464.95</v>
+        <v>716.25</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>461.97</v>
+        <v>713.25</v>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>SMA 20</t>
+          <t>Swing Low</t>
         </is>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.65</v>
+        <v>0.42</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>50.4</v>
+        <v>44.4</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>7.1</v>
+        <v>4.9</v>
       </c>
       <c r="K6" s="4" t="inlineStr">
         <is>
@@ -2529,17 +2529,17 @@
       </c>
       <c r="M6" s="4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="N6" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O6" s="4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="P6" s="4" t="inlineStr">
@@ -2554,65 +2554,65 @@
       </c>
       <c r="R6" s="4" t="inlineStr">
         <is>
-          <t>₹457.35–471.21</t>
+          <t>₹706.12–727.51</t>
         </is>
       </c>
       <c r="S6" s="4" t="n">
-        <v>524</v>
+        <v>773.55</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>448.11</v>
+        <v>691.85</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>3.5</v>
+        <v>2.4</v>
       </c>
       <c r="V6" s="5" t="n">
         <v>8</v>
       </c>
       <c r="W6" s="4" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:DELHIVERY</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:INDHOTEL</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>BHARATFORG</t>
+          <t>TECHM</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>Bharat Forge</t>
+          <t>Tech Mahindra</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>2042.8</v>
+        <v>1625.8</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>2028</v>
+        <v>1616</v>
       </c>
       <c r="F7" s="6" t="inlineStr">
         <is>
-          <t>Swing Low</t>
+          <t>SMA 20</t>
         </is>
       </c>
       <c r="G7" s="6" t="n">
-        <v>0.73</v>
+        <v>0.61</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>11</v>
+        <v>3.3</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>42.9</v>
+        <v>57.5</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>2.3</v>
+        <v>4.9</v>
       </c>
       <c r="K7" s="6" t="inlineStr">
         <is>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="O7" s="6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P7" s="6" t="inlineStr">
@@ -2646,70 +2646,70 @@
       </c>
       <c r="Q7" s="6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="R7" s="6" t="inlineStr">
         <is>
-          <t>₹2007.72–2068.56</t>
+          <t>₹1599.84–1648.32</t>
         </is>
       </c>
       <c r="S7" s="6" t="n">
-        <v>2295</v>
+        <v>1755.86</v>
       </c>
       <c r="T7" s="6" t="n">
-        <v>1967.16</v>
+        <v>1567.52</v>
       </c>
       <c r="U7" s="6" t="n">
-        <v>3.3</v>
+        <v>2.2</v>
       </c>
       <c r="V7" s="5" t="n">
         <v>8</v>
       </c>
       <c r="W7" s="6" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:BHARATFORG</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:TECHM</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>MOTHERSON</t>
+          <t>INDIGO</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Motherson Sumi</t>
+          <t>IndiGo</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>Automobile</t>
+          <t>Aviation</t>
         </is>
       </c>
       <c r="D8" s="4" t="n">
-        <v>165.9</v>
+        <v>5101.5</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>165.85</v>
+        <v>5064.5</v>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>SMA 20</t>
+          <t>Swing Low</t>
         </is>
       </c>
       <c r="G8" s="4" t="n">
-        <v>0.03</v>
+        <v>0.73</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>4.3</v>
+        <v>7.4</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>60.3</v>
+        <v>42.4</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>2.7</v>
+        <v>4.4</v>
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="L8" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="M8" s="4" t="inlineStr">
@@ -2743,74 +2743,74 @@
       </c>
       <c r="Q8" s="4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="R8" s="4" t="inlineStr">
         <is>
-          <t>₹164.19–169.16</t>
+          <t>₹5013.85–5165.79</t>
         </is>
       </c>
       <c r="S8" s="4" t="n">
-        <v>179.17</v>
+        <v>5509.62</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>160.87</v>
+        <v>4912.56</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>2.7</v>
+        <v>2.2</v>
       </c>
       <c r="V8" s="5" t="n">
         <v>8</v>
       </c>
       <c r="W8" s="4" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:MOTHERSON</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:INDIGO</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>KFINTECH</t>
+          <t>NMDC</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>KFin Technologies</t>
+          <t>NMDC</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Metals &amp; Mining</t>
         </is>
       </c>
       <c r="D9" s="6" t="n">
-        <v>951</v>
+        <v>86.06999999999999</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>950.41</v>
+        <v>85.38</v>
       </c>
       <c r="F9" s="6" t="inlineStr">
         <is>
-          <t>SMA 200</t>
+          <t>SMA 50</t>
         </is>
       </c>
       <c r="G9" s="6" t="n">
-        <v>0.06</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>52.9</v>
+        <v>52.7</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="K9" s="6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L9" s="6" t="inlineStr">
@@ -2830,63 +2830,63 @@
       </c>
       <c r="O9" s="6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P9" s="6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="Q9" s="6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="R9" s="6" t="inlineStr">
         <is>
-          <t>₹940.9–969.42</t>
+          <t>₹84.52–87.09</t>
         </is>
       </c>
       <c r="S9" s="6" t="n">
-        <v>1027.08</v>
+        <v>92.95999999999999</v>
       </c>
       <c r="T9" s="6" t="n">
-        <v>921.9</v>
+        <v>82.81999999999999</v>
       </c>
       <c r="U9" s="6" t="n">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
       <c r="V9" s="5" t="n">
         <v>8</v>
       </c>
       <c r="W9" s="6" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:KFINTECH</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:NMDC</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>TECHM</t>
+          <t>SONACOMS</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Tech Mahindra</t>
+          <t>Sona BLW</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>Capital Goods</t>
         </is>
       </c>
       <c r="D10" s="4" t="n">
-        <v>1620</v>
+        <v>816.35</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>1615.71</v>
+        <v>809.01</v>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
@@ -2894,16 +2894,16 @@
         </is>
       </c>
       <c r="G10" s="4" t="n">
-        <v>0.27</v>
+        <v>0.91</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>56.1</v>
+        <v>62.8</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>4.9</v>
+        <v>3.6</v>
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
@@ -2942,48 +2942,48 @@
       </c>
       <c r="R10" s="4" t="inlineStr">
         <is>
-          <t>₹1599.55–1648.02</t>
+          <t>₹800.92–825.2</t>
         </is>
       </c>
       <c r="S10" s="4" t="n">
-        <v>1749.6</v>
+        <v>881.66</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>1567.24</v>
+        <v>784.74</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="V10" s="5" t="n">
         <v>8</v>
       </c>
       <c r="W10" s="4" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:TECHM</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:SONACOMS</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>MPHASIS</t>
+          <t>M&amp;M</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>Mphasis</t>
+          <t>Mahindra &amp; Mahindra</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>Automobile</t>
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>2415.1</v>
+        <v>3346.3</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>2404.28</v>
+        <v>3314.39</v>
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
@@ -2991,16 +2991,16 @@
         </is>
       </c>
       <c r="G11" s="6" t="n">
-        <v>0.45</v>
+        <v>0.96</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>49.5</v>
+        <v>48.7</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="K11" s="6" t="inlineStr">
         <is>
@@ -3039,62 +3039,62 @@
       </c>
       <c r="R11" s="6" t="inlineStr">
         <is>
-          <t>₹2380.24–2452.37</t>
+          <t>₹3281.24–3380.67</t>
         </is>
       </c>
       <c r="S11" s="6" t="n">
-        <v>2608.31</v>
+        <v>3614</v>
       </c>
       <c r="T11" s="6" t="n">
-        <v>2332.15</v>
+        <v>3214.95</v>
       </c>
       <c r="U11" s="6" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="V11" s="5" t="n">
         <v>8</v>
       </c>
       <c r="W11" s="6" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:MPHASIS</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:M&amp;M</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>SONACOMS</t>
+          <t>GAIL</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Sona BLW</t>
+          <t>GAIL India</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Oil &amp; Gas</t>
         </is>
       </c>
       <c r="D12" s="4" t="n">
-        <v>813.05</v>
+        <v>172.35</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>808.85</v>
+        <v>170.7</v>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>SMA 20</t>
+          <t>Swing Low</t>
         </is>
       </c>
       <c r="G12" s="4" t="n">
-        <v>0.52</v>
+        <v>0.97</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>61.5</v>
+        <v>47.3</v>
       </c>
       <c r="J12" s="4" t="n">
         <v>3.6</v>
@@ -3106,7 +3106,7 @@
       </c>
       <c r="L12" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="M12" s="4" t="inlineStr">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="O12" s="4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="P12" s="4" t="inlineStr">
@@ -3136,65 +3136,65 @@
       </c>
       <c r="R12" s="4" t="inlineStr">
         <is>
-          <t>₹800.76–825.03</t>
+          <t>₹168.99–174.11</t>
         </is>
       </c>
       <c r="S12" s="4" t="n">
-        <v>878.09</v>
+        <v>186.14</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>784.58</v>
+        <v>165.58</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="V12" s="5" t="n">
         <v>8</v>
       </c>
       <c r="W12" s="4" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:SONACOMS</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:GAIL</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>IDFCFIRSTB</t>
+          <t>OBEROIRLTY</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>IDFC First Bank</t>
+          <t>Oberoi Realty</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>84.3</v>
+        <v>1867.4</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>83.61</v>
+        <v>1844.78</v>
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
-          <t>Swing Low</t>
+          <t>SMA 50</t>
         </is>
       </c>
       <c r="G13" s="6" t="n">
-        <v>0.83</v>
+        <v>1.23</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>3</v>
+        <v>4.8</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>51.2</v>
+        <v>53.1</v>
       </c>
       <c r="J13" s="6" t="n">
-        <v>4.9</v>
+        <v>3.4</v>
       </c>
       <c r="K13" s="6" t="inlineStr">
         <is>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="M13" s="6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N13" s="6" t="inlineStr">
@@ -3228,53 +3228,53 @@
       </c>
       <c r="Q13" s="6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="R13" s="6" t="inlineStr">
         <is>
-          <t>₹82.77–85.28</t>
+          <t>₹1826.33–1881.67</t>
         </is>
       </c>
       <c r="S13" s="6" t="n">
-        <v>91.04000000000001</v>
+        <v>2016.79</v>
       </c>
       <c r="T13" s="6" t="n">
-        <v>81.09999999999999</v>
+        <v>1789.43</v>
       </c>
       <c r="U13" s="6" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="V13" s="5" t="n">
         <v>8</v>
       </c>
       <c r="W13" s="6" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:IDFCFIRSTB</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:OBEROIRLTY</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>OBEROIRLTY</t>
+          <t>RBLBANK</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Oberoi Realty</t>
+          <t>RBL Bank</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D14" s="4" t="n">
-        <v>1860.2</v>
+        <v>381.15</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>1844.41</v>
+        <v>376.4</v>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
@@ -3282,16 +3282,16 @@
         </is>
       </c>
       <c r="G14" s="4" t="n">
-        <v>0.86</v>
+        <v>1.26</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>5.1</v>
+        <v>3.4</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>51.8</v>
+        <v>50.1</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
@@ -3330,65 +3330,65 @@
       </c>
       <c r="R14" s="4" t="inlineStr">
         <is>
-          <t>₹1825.97–1881.3</t>
+          <t>₹372.64–383.93</t>
         </is>
       </c>
       <c r="S14" s="4" t="n">
-        <v>2009.02</v>
+        <v>411.64</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>1789.08</v>
+        <v>365.11</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="V14" s="5" t="n">
         <v>8</v>
       </c>
       <c r="W14" s="4" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:OBEROIRLTY</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:RBLBANK</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>INDIGO</t>
+          <t>PIDILITIND</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Pidilite Industries</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>Aviation</t>
+          <t>Chemicals</t>
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>5110</v>
+        <v>1637.6</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>5064.5</v>
+        <v>1616.42</v>
       </c>
       <c r="F15" s="6" t="inlineStr">
         <is>
-          <t>Swing Low</t>
+          <t>SMA 50</t>
         </is>
       </c>
       <c r="G15" s="6" t="n">
-        <v>0.9</v>
+        <v>1.31</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>7.2</v>
+        <v>4.1</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>42.9</v>
+        <v>48.8</v>
       </c>
       <c r="J15" s="6" t="n">
-        <v>4.4</v>
+        <v>3.5</v>
       </c>
       <c r="K15" s="6" t="inlineStr">
         <is>
@@ -3397,7 +3397,7 @@
       </c>
       <c r="L15" s="6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="M15" s="6" t="inlineStr">
@@ -3422,41 +3422,41 @@
       </c>
       <c r="Q15" s="6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="R15" s="6" t="inlineStr">
         <is>
-          <t>₹5013.85–5165.79</t>
+          <t>₹1600.25–1648.74</t>
         </is>
       </c>
       <c r="S15" s="6" t="n">
-        <v>5518.8</v>
+        <v>1768.61</v>
       </c>
       <c r="T15" s="6" t="n">
-        <v>4912.56</v>
+        <v>1567.92</v>
       </c>
       <c r="U15" s="6" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="V15" s="5" t="n">
         <v>8</v>
       </c>
       <c r="W15" s="6" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:INDIGO</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:PIDILITIND</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>GAIL</t>
+          <t>OIL</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>GAIL India</t>
+          <t>Oil India</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -3465,27 +3465,27 @@
         </is>
       </c>
       <c r="D16" s="4" t="n">
-        <v>172.32</v>
+        <v>483.3</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>170.7</v>
+        <v>472.3</v>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>Swing Low</t>
+          <t>SMA 20</t>
         </is>
       </c>
       <c r="G16" s="4" t="n">
-        <v>0.95</v>
+        <v>2.33</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>47.2</v>
+        <v>62.2</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>3.6</v>
+        <v>8.5</v>
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
@@ -3509,7 +3509,7 @@
       </c>
       <c r="O16" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P16" s="4" t="inlineStr">
@@ -3519,74 +3519,74 @@
       </c>
       <c r="Q16" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="R16" s="4" t="inlineStr">
         <is>
-          <t>₹168.99–174.11</t>
+          <t>₹467.58–481.75</t>
         </is>
       </c>
       <c r="S16" s="4" t="n">
-        <v>186.11</v>
+        <v>521.96</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>165.58</v>
+        <v>458.13</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>2.1</v>
+        <v>1.5</v>
       </c>
       <c r="V16" s="5" t="n">
         <v>8</v>
       </c>
       <c r="W16" s="4" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:GAIL</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:OIL</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>NMDC</t>
+          <t>PHOENIXLTD</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>NMDC</t>
+          <t>Phoenix Mills</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>Metals &amp; Mining</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>86.20999999999999</v>
+        <v>1891.5</v>
       </c>
       <c r="E17" s="6" t="n">
-        <v>85.38</v>
+        <v>1877.3</v>
       </c>
       <c r="F17" s="6" t="inlineStr">
         <is>
-          <t>SMA 50</t>
+          <t>Swing Low</t>
         </is>
       </c>
       <c r="G17" s="6" t="n">
-        <v>0.97</v>
+        <v>0.76</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>3.2</v>
+        <v>3.9</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>53.2</v>
+        <v>41.3</v>
       </c>
       <c r="J17" s="6" t="n">
-        <v>4.6</v>
+        <v>3.8</v>
       </c>
       <c r="K17" s="6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L17" s="6" t="inlineStr">
@@ -3606,12 +3606,12 @@
       </c>
       <c r="O17" s="6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="P17" s="6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Q17" s="6" t="inlineStr">
@@ -3621,145 +3621,145 @@
       </c>
       <c r="R17" s="6" t="inlineStr">
         <is>
-          <t>₹84.53–87.09</t>
+          <t>₹1858.53–1914.85</t>
         </is>
       </c>
       <c r="S17" s="6" t="n">
-        <v>93.11</v>
+        <v>2169.8</v>
       </c>
       <c r="T17" s="6" t="n">
-        <v>82.81999999999999</v>
+        <v>1820.98</v>
       </c>
       <c r="U17" s="6" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="V17" s="5" t="n">
-        <v>8</v>
+        <v>4</v>
+      </c>
+      <c r="V17" s="7" t="n">
+        <v>7</v>
       </c>
       <c r="W17" s="6" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:NMDC</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:PHOENIXLTD</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>PIDILITIND</t>
+          <t>BHARATFORG</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>Pidilite Industries</t>
+          <t>Bharat Forge</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Capital Goods</t>
         </is>
       </c>
       <c r="D18" s="4" t="n">
-        <v>1640</v>
+        <v>2040.6</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>1616.46</v>
+        <v>2028</v>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>SMA 50</t>
+          <t>Swing Low</t>
         </is>
       </c>
       <c r="G18" s="4" t="n">
-        <v>1.46</v>
+        <v>0.62</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>4</v>
+        <v>11.1</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>49.4</v>
+        <v>42.5</v>
       </c>
       <c r="J18" s="4" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="K18" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L18" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M18" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N18" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O18" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="P18" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q18" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R18" s="4" t="inlineStr">
+        <is>
+          <t>₹2007.72–2068.56</t>
+        </is>
+      </c>
+      <c r="S18" s="4" t="n">
+        <v>2295</v>
+      </c>
+      <c r="T18" s="4" t="n">
+        <v>1967.16</v>
+      </c>
+      <c r="U18" s="4" t="n">
         <v>3.5</v>
       </c>
-      <c r="K18" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L18" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M18" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="N18" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O18" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="P18" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Q18" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R18" s="4" t="inlineStr">
-        <is>
-          <t>₹1600.3–1648.79</t>
-        </is>
-      </c>
-      <c r="S18" s="4" t="n">
-        <v>1771.2</v>
-      </c>
-      <c r="T18" s="4" t="n">
-        <v>1567.97</v>
-      </c>
-      <c r="U18" s="4" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="V18" s="5" t="n">
-        <v>8</v>
+      <c r="V18" s="7" t="n">
+        <v>7</v>
       </c>
       <c r="W18" s="4" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:PIDILITIND</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:BHARATFORG</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>RBLBANK</t>
+          <t>NESTLEIND</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>RBL Bank</t>
+          <t>Nestle India</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Consumer Goods</t>
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>381.9</v>
+        <v>1448.4</v>
       </c>
       <c r="E19" s="6" t="n">
-        <v>376.4</v>
+        <v>1448.3</v>
       </c>
       <c r="F19" s="6" t="inlineStr">
         <is>
@@ -3767,16 +3767,16 @@
         </is>
       </c>
       <c r="G19" s="6" t="n">
-        <v>1.46</v>
+        <v>0.01</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>3.2</v>
+        <v>6.7</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>51</v>
+        <v>42.2</v>
       </c>
       <c r="J19" s="6" t="n">
-        <v>2.9</v>
+        <v>3.5</v>
       </c>
       <c r="K19" s="6" t="inlineStr">
         <is>
@@ -3785,7 +3785,7 @@
       </c>
       <c r="L19" s="6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="M19" s="6" t="inlineStr">
@@ -3815,65 +3815,65 @@
       </c>
       <c r="R19" s="6" t="inlineStr">
         <is>
-          <t>₹372.64–383.93</t>
+          <t>₹1433.82–1477.27</t>
         </is>
       </c>
       <c r="S19" s="6" t="n">
-        <v>412.45</v>
+        <v>1564.27</v>
       </c>
       <c r="T19" s="6" t="n">
-        <v>365.11</v>
+        <v>1404.85</v>
       </c>
       <c r="U19" s="6" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="V19" s="5" t="n">
-        <v>8</v>
+        <v>2.7</v>
+      </c>
+      <c r="V19" s="7" t="n">
+        <v>7</v>
       </c>
       <c r="W19" s="6" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:RBLBANK</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:NESTLEIND</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>PHOENIXLTD</t>
+          <t>ASHOKLEY</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>Phoenix Mills</t>
+          <t>Ashok Leyland</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Automobile</t>
         </is>
       </c>
       <c r="D20" s="4" t="n">
-        <v>1889.3</v>
+        <v>175.67</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>1877.3</v>
+        <v>175.34</v>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>Swing Low</t>
+          <t>SMA 20</t>
         </is>
       </c>
       <c r="G20" s="4" t="n">
-        <v>0.64</v>
+        <v>0.19</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>40.9</v>
+        <v>57.8</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>4.5</v>
+        <v>5.8</v>
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
@@ -3882,12 +3882,12 @@
       </c>
       <c r="L20" s="4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="M20" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N20" s="4" t="inlineStr">
@@ -3897,7 +3897,7 @@
       </c>
       <c r="O20" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P20" s="4" t="inlineStr">
@@ -3912,24 +3912,24 @@
       </c>
       <c r="R20" s="4" t="inlineStr">
         <is>
-          <t>₹1858.53–1914.85</t>
+          <t>₹173.58–178.84</t>
         </is>
       </c>
       <c r="S20" s="4" t="n">
-        <v>2169.8</v>
+        <v>189.72</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>1820.98</v>
+        <v>170.07</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>4.1</v>
+        <v>2.5</v>
       </c>
       <c r="V20" s="7" t="n">
         <v>7</v>
       </c>
       <c r="W20" s="4" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:PHOENIXLTD</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:ASHOKLEY</t>
         </is>
       </c>
     </row>
@@ -3950,7 +3950,7 @@
         </is>
       </c>
       <c r="D21" s="6" t="n">
-        <v>1985</v>
+        <v>1989.8</v>
       </c>
       <c r="E21" s="6" t="n">
         <v>1985</v>
@@ -3961,16 +3961,16 @@
         </is>
       </c>
       <c r="G21" s="6" t="n">
-        <v>0</v>
+        <v>0.24</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>6.3</v>
+        <v>6.1</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>49.5</v>
+        <v>50.6</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="K21" s="6" t="inlineStr">
         <is>
@@ -4013,13 +4013,13 @@
         </is>
       </c>
       <c r="S21" s="6" t="n">
-        <v>2143.8</v>
+        <v>2148.98</v>
       </c>
       <c r="T21" s="6" t="n">
         <v>1925.45</v>
       </c>
       <c r="U21" s="6" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="V21" s="7" t="n">
         <v>7</v>
@@ -4190,51 +4190,51 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>M&amp;M</t>
+          <t>BAJAJFINSV</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Mahindra &amp; Mahindra</t>
+          <t>Bajaj Finserv</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>Automobile</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D2" s="4" t="n">
-        <v>3354.7</v>
+        <v>1989.8</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>3552.27</v>
+        <v>2129.09</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>5.89</v>
+        <v>7</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>3739.27</v>
+        <v>2244.29</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>3263.4</v>
+        <v>1950</v>
       </c>
       <c r="I2" s="4" t="n">
-        <v>2.7</v>
+        <v>2</v>
       </c>
       <c r="J2" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>3.37</v>
+        <v>2.15</v>
       </c>
       <c r="L2" s="4" t="n">
-        <v>5.33</v>
+        <v>6.01</v>
       </c>
       <c r="M2" s="4" t="n">
-        <v>0.82</v>
+        <v>0.49</v>
       </c>
       <c r="N2" s="4" t="n">
-        <v>49.7</v>
+        <v>50.6</v>
       </c>
       <c r="O2" s="4" t="inlineStr">
         <is>
@@ -4276,19 +4276,19 @@
       </c>
       <c r="W2" s="4" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:M&amp;M</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:BAJAJFINSV</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
         <is>
-          <t>BAJAJFINSV</t>
+          <t>CHOLAFIN</t>
         </is>
       </c>
       <c r="B3" s="6" t="inlineStr">
         <is>
-          <t>Bajaj Finserv</t>
+          <t>Cholamandalam Investment</t>
         </is>
       </c>
       <c r="C3" s="6" t="inlineStr">
@@ -4297,37 +4297,37 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>1985</v>
+        <v>1835.1</v>
       </c>
       <c r="E3" s="6" t="n">
-        <v>2129.09</v>
+        <v>1962.26</v>
       </c>
       <c r="F3" s="6" t="n">
-        <v>7.26</v>
+        <v>6.93</v>
       </c>
       <c r="G3" s="6" t="n">
-        <v>2230.09</v>
+        <v>2067.16</v>
       </c>
       <c r="H3" s="6" t="n">
-        <v>1945.3</v>
+        <v>1798.4</v>
       </c>
       <c r="I3" s="6" t="n">
         <v>2</v>
       </c>
       <c r="J3" s="6" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="K3" s="6" t="n">
-        <v>2.39</v>
+        <v>2.93</v>
       </c>
       <c r="L3" s="6" t="n">
-        <v>6.07</v>
+        <v>5.71</v>
       </c>
       <c r="M3" s="6" t="n">
-        <v>0.5</v>
+        <v>0.84</v>
       </c>
       <c r="N3" s="6" t="n">
-        <v>49.5</v>
+        <v>47</v>
       </c>
       <c r="O3" s="6" t="inlineStr">
         <is>
@@ -4369,58 +4369,58 @@
       </c>
       <c r="W3" s="6" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:BAJAJFINSV</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:CHOLAFIN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>BAJFINANCE</t>
+          <t>M&amp;M</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>Bajaj Finance</t>
+          <t>Mahindra &amp; Mahindra</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Automobile</t>
         </is>
       </c>
       <c r="D4" s="4" t="n">
-        <v>1064.4</v>
+        <v>3346.3</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>1118.56</v>
+        <v>3552.27</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>5.09</v>
+        <v>6.16</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>1156.36</v>
+        <v>3739.27</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>1043.11</v>
+        <v>3263.4</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>2.87</v>
+        <v>3.38</v>
       </c>
       <c r="L4" s="4" t="n">
-        <v>8.9</v>
+        <v>5.4</v>
       </c>
       <c r="M4" s="4" t="n">
-        <v>0.76</v>
+        <v>0.79</v>
       </c>
       <c r="N4" s="4" t="n">
-        <v>45.5</v>
+        <v>48.7</v>
       </c>
       <c r="O4" s="4" t="inlineStr">
         <is>
@@ -4462,58 +4462,58 @@
       </c>
       <c r="W4" s="4" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:BAJFINANCE</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:M&amp;M</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>PIDILITIND</t>
+          <t>BAJFINANCE</t>
         </is>
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>Pidilite Industries</t>
+          <t>Bajaj Finance</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>1640</v>
+        <v>1065.6</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>1716.04</v>
+        <v>1118.56</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>4.64</v>
+        <v>4.97</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>1806.24</v>
+        <v>1155.16</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>1579.07</v>
+        <v>1044.29</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>3.7</v>
+        <v>2</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>2.71</v>
+        <v>2.76</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>5.21</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>0.72</v>
+        <v>0.74</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>49.4</v>
+        <v>45.8</v>
       </c>
       <c r="O5" s="6" t="inlineStr">
         <is>
@@ -4522,7 +4522,7 @@
       </c>
       <c r="P5" s="6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="Q5" s="6" t="inlineStr">
@@ -4551,62 +4551,62 @@
         </is>
       </c>
       <c r="V5" s="5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W5" s="6" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:PIDILITIND</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:BAJFINANCE</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>BAJAJ-AUTO</t>
+          <t>PIDILITIND</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Bajaj Auto</t>
+          <t>Pidilite Industries</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>Automobile</t>
+          <t>Chemicals</t>
         </is>
       </c>
       <c r="D6" s="4" t="n">
-        <v>11997</v>
+        <v>1637.6</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>12100.2</v>
+        <v>1716.04</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.86</v>
+        <v>4.79</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>12759.2</v>
+        <v>1806.24</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>11111.24</v>
+        <v>1579.07</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>7.4</v>
+        <v>3.6</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>3.25</v>
+        <v>2.72</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>3.63</v>
+        <v>5.25</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>0.97</v>
+        <v>0.67</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>66.5</v>
+        <v>48.8</v>
       </c>
       <c r="O6" s="4" t="inlineStr">
         <is>
@@ -4625,7 +4625,7 @@
       </c>
       <c r="R6" s="4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="S6" s="4" t="inlineStr">
@@ -4648,58 +4648,58 @@
       </c>
       <c r="W6" s="4" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:BAJAJ-AUTO</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:PIDILITIND</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>RBLBANK</t>
+          <t>BAJAJ-AUTO</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>RBL Bank</t>
+          <t>Bajaj Auto</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Automobile</t>
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>381.9</v>
+        <v>11995</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>396.47</v>
+        <v>12100.2</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>3.82</v>
+        <v>0.88</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>418.78</v>
+        <v>12757.2</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>362.79</v>
+        <v>11111.24</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>5</v>
+        <v>7.4</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K7" s="6" t="n">
-        <v>2.88</v>
+        <v>3.23</v>
       </c>
       <c r="L7" s="6" t="n">
-        <v>4</v>
+        <v>3.63</v>
       </c>
       <c r="M7" s="6" t="n">
-        <v>0.71</v>
+        <v>0.95</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>51</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="O7" s="6" t="inlineStr">
         <is>
@@ -4718,7 +4718,7 @@
       </c>
       <c r="R7" s="6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="S7" s="6" t="inlineStr">
@@ -4741,58 +4741,58 @@
       </c>
       <c r="W7" s="6" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:RBLBANK</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:BAJAJ-AUTO</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>TVSMOTOR</t>
+          <t>RBLBANK</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>TVS Motor</t>
+          <t>RBL Bank</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>Automobile</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D8" s="4" t="n">
-        <v>4322</v>
+        <v>381.15</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>4506.92</v>
+        <v>396.47</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>4.28</v>
+        <v>4.02</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>4764.72</v>
+        <v>418.78</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>4124.23</v>
+        <v>362.79</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>3.7</v>
+        <v>2.98</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>4.28</v>
+        <v>4.05</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>1.29</v>
+        <v>0.66</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>55.3</v>
+        <v>50.1</v>
       </c>
       <c r="O8" s="4" t="inlineStr">
         <is>
@@ -4801,7 +4801,7 @@
       </c>
       <c r="P8" s="4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Q8" s="4" t="inlineStr">
@@ -4834,62 +4834,62 @@
       </c>
       <c r="W8" s="4" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:TVSMOTOR</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:RBLBANK</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>TITAN</t>
+          <t>TVSMOTOR</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>Titan Company</t>
+          <t>TVS Motor</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>Consumer Goods</t>
+          <t>Automobile</t>
         </is>
       </c>
       <c r="D9" s="6" t="n">
-        <v>5130</v>
+        <v>4322.9</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>5212.63</v>
+        <v>4506.92</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>1.61</v>
+        <v>4.26</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>5506.63</v>
+        <v>4764.72</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>4777.7</v>
+        <v>4124.23</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>6.9</v>
+        <v>4.6</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K9" s="6" t="n">
-        <v>2.35</v>
+        <v>3.7</v>
       </c>
       <c r="L9" s="6" t="n">
-        <v>5.36</v>
+        <v>4.28</v>
       </c>
       <c r="M9" s="6" t="n">
-        <v>0.63</v>
+        <v>1.25</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>66.09999999999999</v>
+        <v>55.4</v>
       </c>
       <c r="O9" s="6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P9" s="6" t="inlineStr">
@@ -4927,62 +4927,62 @@
       </c>
       <c r="W9" s="6" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:TITAN</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:TVSMOTOR</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>SUNPHARMA</t>
+          <t>TITAN</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Sun Pharma</t>
+          <t>Titan Company</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>Pharma</t>
+          <t>Consumer Goods</t>
         </is>
       </c>
       <c r="D10" s="4" t="n">
-        <v>1925</v>
+        <v>5125.9</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>2057.13</v>
+        <v>5212.63</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>6.86</v>
+        <v>1.69</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>2172.53</v>
+        <v>5506.63</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>1837.6</v>
+        <v>4777.7</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>4.5</v>
+        <v>6.8</v>
       </c>
       <c r="J10" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>2.59</v>
+        <v>2.35</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>4.82</v>
+        <v>5.35</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0.72</v>
+        <v>0.61</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>51.3</v>
+        <v>65.5</v>
       </c>
       <c r="O10" s="4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="P10" s="4" t="inlineStr">
@@ -5002,7 +5002,7 @@
       </c>
       <c r="S10" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="T10" s="4" t="inlineStr">
@@ -5020,58 +5020,58 @@
       </c>
       <c r="W10" s="4" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:SUNPHARMA</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:TITAN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>CHOLAFIN</t>
+          <t>SUNPHARMA</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>Cholamandalam Investment</t>
+          <t>Sun Pharma</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Pharma</t>
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>1840.5</v>
+        <v>1928.2</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>1962.26</v>
+        <v>2057.13</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>6.62</v>
+        <v>6.69</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>2061.76</v>
+        <v>2172.53</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>1803.69</v>
+        <v>1837.6</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>2</v>
+        <v>4.7</v>
       </c>
       <c r="J11" s="6" t="n">
         <v>22</v>
       </c>
       <c r="K11" s="6" t="n">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="L11" s="6" t="n">
-        <v>5.61</v>
+        <v>4.83</v>
       </c>
       <c r="M11" s="6" t="n">
-        <v>0.89</v>
+        <v>0.7</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>47.9</v>
+        <v>52.2</v>
       </c>
       <c r="O11" s="6" t="inlineStr">
         <is>
@@ -5095,7 +5095,7 @@
       </c>
       <c r="S11" s="6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="T11" s="6" t="inlineStr">
@@ -5113,7 +5113,7 @@
       </c>
       <c r="W11" s="6" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:CHOLAFIN</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:SUNPHARMA</t>
         </is>
       </c>
     </row>
@@ -5134,13 +5134,13 @@
         </is>
       </c>
       <c r="D12" s="4" t="n">
-        <v>114.56</v>
+        <v>114.74</v>
       </c>
       <c r="E12" s="4" t="n">
         <v>120.1</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>4.84</v>
+        <v>4.67</v>
       </c>
       <c r="G12" s="4" t="n">
         <v>126.37</v>
@@ -5149,22 +5149,22 @@
         <v>110.46</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="J12" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>3</v>
+        <v>2.84</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>5.54</v>
+        <v>5.52</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.85</v>
+        <v>0.82</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>50.6</v>
+        <v>51.3</v>
       </c>
       <c r="O12" s="4" t="inlineStr">
         <is>
@@ -5213,60 +5213,60 @@
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>SONACOMS</t>
+          <t>SBIN</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>Sona BLW</t>
+          <t>State Bank of India</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>813.05</v>
+        <v>1045.1</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>848.22</v>
+        <v>1130.12</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>4.33</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>887.22</v>
+        <v>1187.82</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>769.3</v>
+        <v>1018.71</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>5.4</v>
+        <v>2.5</v>
       </c>
       <c r="J13" s="6" t="n">
         <v>21</v>
       </c>
       <c r="K13" s="6" t="n">
-        <v>3.57</v>
+        <v>1.29</v>
       </c>
       <c r="L13" s="6" t="n">
-        <v>5.45</v>
+        <v>6.15</v>
       </c>
       <c r="M13" s="6" t="n">
-        <v>0.72</v>
+        <v>0.6</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>61.5</v>
+        <v>48.3</v>
       </c>
       <c r="O13" s="6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P13" s="6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Q13" s="6" t="inlineStr">
@@ -5299,67 +5299,67 @@
       </c>
       <c r="W13" s="6" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:SONACOMS</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:SBIN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>360ONE</t>
+          <t>SONACOMS</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>360 ONE WAM</t>
+          <t>Sona BLW</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Capital Goods</t>
         </is>
       </c>
       <c r="D14" s="4" t="n">
-        <v>1170</v>
+        <v>816.35</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>1229.01</v>
+        <v>848.22</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>5.04</v>
+        <v>3.9</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>1291.21</v>
+        <v>887.22</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>1124.84</v>
+        <v>769.3</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>3.9</v>
+        <v>5.8</v>
       </c>
       <c r="J14" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>3.97</v>
+        <v>3.55</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>5.28</v>
+        <v>5.49</v>
       </c>
       <c r="M14" s="4" t="n">
         <v>0.7</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>49.8</v>
+        <v>62.8</v>
       </c>
       <c r="O14" s="4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="P14" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="Q14" s="4" t="inlineStr">
@@ -5392,67 +5392,67 @@
       </c>
       <c r="W14" s="4" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:360ONE</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:SONACOMS</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>UNOMINDA</t>
+          <t>360ONE</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>UNO Minda</t>
+          <t>360 ONE WAM</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>Automobile</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>1280</v>
+        <v>1175</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>1304.79</v>
+        <v>1229.01</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>1.94</v>
+        <v>4.6</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>1365.79</v>
+        <v>1291.21</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>1202.46</v>
+        <v>1124.84</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>6.1</v>
+        <v>4.3</v>
       </c>
       <c r="J15" s="6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K15" s="6" t="n">
-        <v>2.24</v>
+        <v>3.95</v>
       </c>
       <c r="L15" s="6" t="n">
-        <v>5.56</v>
+        <v>5.23</v>
       </c>
       <c r="M15" s="6" t="n">
-        <v>0.78</v>
+        <v>0.65</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>64.90000000000001</v>
+        <v>51.1</v>
       </c>
       <c r="O15" s="6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P15" s="6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Q15" s="6" t="inlineStr">
@@ -5485,58 +5485,58 @@
       </c>
       <c r="W15" s="6" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:UNOMINDA</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:360ONE</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>PNBHOUSING</t>
+          <t>UNOMINDA</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>PNB Housing Finance</t>
+          <t>UNO Minda</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Automobile</t>
         </is>
       </c>
       <c r="D16" s="4" t="n">
-        <v>1145.4</v>
+        <v>1280.8</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>1217.56</v>
+        <v>1304.79</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>6.3</v>
+        <v>1.87</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>1280.96</v>
+        <v>1365.79</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>1099.17</v>
+        <v>1202.46</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>4</v>
+        <v>6.1</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>3.46</v>
+        <v>2.3</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>8.09</v>
+        <v>5.57</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.77</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>52.3</v>
+        <v>65</v>
       </c>
       <c r="O16" s="4" t="inlineStr">
         <is>
@@ -5578,58 +5578,58 @@
       </c>
       <c r="W16" s="4" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:PNBHOUSING</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:UNOMINDA</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>MOTHERSON</t>
+          <t>PNBHOUSING</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>Motherson Sumi</t>
+          <t>PNB Housing Finance</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>Automobile</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>165.9</v>
+        <v>1153.4</v>
       </c>
       <c r="E17" s="6" t="n">
-        <v>174.14</v>
+        <v>1217.56</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>4.97</v>
+        <v>5.56</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>179.54</v>
+        <v>1280.96</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>161.7</v>
+        <v>1099.17</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>2.5</v>
+        <v>4.7</v>
       </c>
       <c r="J17" s="6" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="K17" s="6" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="L17" s="6" t="n">
-        <v>13.19</v>
+        <v>8.06</v>
       </c>
       <c r="M17" s="6" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.54</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>60.3</v>
+        <v>54.8</v>
       </c>
       <c r="O17" s="6" t="inlineStr">
         <is>
@@ -5671,62 +5671,62 @@
       </c>
       <c r="W17" s="6" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:MOTHERSON</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:PNBHOUSING</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>DLF</t>
+          <t>MOTHERSON</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>DLF</t>
+          <t>Motherson Sumi</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Automobile</t>
         </is>
       </c>
       <c r="D18" s="4" t="n">
-        <v>668</v>
+        <v>165.06</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>693.85</v>
+        <v>174.14</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>3.87</v>
+        <v>5.5</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>732.75</v>
+        <v>179.54</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>637.1</v>
+        <v>161.7</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>4.6</v>
+        <v>2</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>3.48</v>
+        <v>3.27</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>8.17</v>
+        <v>13.2</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>0.58</v>
+        <v>0.53</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>51.8</v>
+        <v>58.2</v>
       </c>
       <c r="O18" s="4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="P18" s="4" t="inlineStr">
@@ -5746,7 +5746,7 @@
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="T18" s="4" t="inlineStr">
@@ -5764,58 +5764,58 @@
       </c>
       <c r="W18" s="4" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:DLF</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:MOTHERSON</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>APOLLOHOSP</t>
+          <t>DLF</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>Apollo Hospitals</t>
+          <t>DLF</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>8849.5</v>
+        <v>671.2</v>
       </c>
       <c r="E19" s="6" t="n">
-        <v>9084.67</v>
+        <v>693.85</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>2.66</v>
+        <v>3.37</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>9560.620000000001</v>
+        <v>732.75</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>8392.26</v>
+        <v>637.1</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J19" s="6" t="n">
-        <v>49</v>
+        <v>16</v>
       </c>
       <c r="K19" s="6" t="n">
-        <v>2.21</v>
+        <v>3.46</v>
       </c>
       <c r="L19" s="6" t="n">
-        <v>5.26</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="M19" s="6" t="n">
-        <v>0.64</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>52.7</v>
+        <v>53.3</v>
       </c>
       <c r="O19" s="6" t="inlineStr">
         <is>
@@ -5829,7 +5829,7 @@
       </c>
       <c r="Q19" s="6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="R19" s="6" t="inlineStr">
@@ -5852,63 +5852,63 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="V19" s="7" t="n">
-        <v>7</v>
+      <c r="V19" s="5" t="n">
+        <v>8</v>
       </c>
       <c r="W19" s="6" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:APOLLOHOSP</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:DLF</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>TORNTPHARM</t>
+          <t>APOLLOHOSP</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>Torrent Pharmaceuticals</t>
+          <t>Apollo Hospitals</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>Pharma</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D20" s="4" t="n">
-        <v>4900.5</v>
+        <v>8836</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>5276.25</v>
+        <v>9084.67</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>7.67</v>
+        <v>2.81</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>5566.05</v>
+        <v>9560.620000000001</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>4736.34</v>
+        <v>8392.26</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>3.3</v>
+        <v>5</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>31</v>
+        <v>49</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>3.34</v>
+        <v>2.22</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>4.66</v>
+        <v>5.26</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>0.78</v>
+        <v>0.61</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>48.4</v>
+        <v>52.1</v>
       </c>
       <c r="O20" s="4" t="inlineStr">
         <is>
@@ -5917,12 +5917,12 @@
       </c>
       <c r="P20" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="Q20" s="4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="R20" s="4" t="inlineStr">
@@ -5932,7 +5932,7 @@
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="T20" s="4" t="inlineStr">
@@ -5950,58 +5950,58 @@
       </c>
       <c r="W20" s="4" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:TORNTPHARM</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:APOLLOHOSP</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>LT</t>
+          <t>TORNTPHARM</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>Larsen &amp; Toubro</t>
+          <t>Torrent Pharmaceuticals</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Pharma</t>
         </is>
       </c>
       <c r="D21" s="6" t="n">
-        <v>4025</v>
+        <v>4930</v>
       </c>
       <c r="E21" s="6" t="n">
-        <v>4145.93</v>
+        <v>5276.25</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>3</v>
+        <v>7.02</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>4333.53</v>
+        <v>5566.05</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>3852.77</v>
+        <v>4736.34</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>4.3</v>
+        <v>3.9</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="K21" s="6" t="n">
-        <v>2.34</v>
+        <v>3.32</v>
       </c>
       <c r="L21" s="6" t="n">
-        <v>2.91</v>
+        <v>4.61</v>
       </c>
       <c r="M21" s="6" t="n">
-        <v>0.88</v>
+        <v>0.73</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>49.7</v>
+        <v>50.1</v>
       </c>
       <c r="O21" s="6" t="inlineStr">
         <is>
@@ -6043,7 +6043,7 @@
       </c>
       <c r="W21" s="6" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE:LT</t>
+          <t>https://www.tradingview.com/chart/?symbol=NSE:TORNTPHARM</t>
         </is>
       </c>
     </row>
